--- a/data/monthly/【2026年5月】月次数値.xlsx
+++ b/data/monthly/【2026年5月】月次数値.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="420" yWindow="600" windowWidth="11232" windowHeight="6492"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="140">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -445,26 +444,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -472,36 +470,36 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -790,14 +788,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y77"/>
-  <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -874,7 +869,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -900,7 +895,7 @@
         <v>2761</v>
       </c>
       <c r="I2">
-        <v>1.303151</v>
+        <v>1.3031509999999999</v>
       </c>
       <c r="J2">
         <v>43.57017544</v>
@@ -927,16 +922,16 @@
         <v>114</v>
       </c>
       <c r="S2">
-        <v>43.570175</v>
+        <v>43.570174999999999</v>
       </c>
       <c r="T2">
-        <v>3.168427</v>
+        <v>3.1684269999999999</v>
       </c>
       <c r="U2">
         <v>127</v>
       </c>
       <c r="V2">
-        <v>3.529739</v>
+        <v>3.5297390000000002</v>
       </c>
       <c r="W2">
         <v>39.110236</v>
@@ -945,10 +940,10 @@
         <v>56</v>
       </c>
       <c r="Y2">
-        <v>88.696429</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+        <v>88.696428999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -977,7 +972,7 @@
         <v>1.37395</v>
       </c>
       <c r="J3">
-        <v>42.77586207</v>
+        <v>42.775862070000002</v>
       </c>
       <c r="K3">
         <v>160</v>
@@ -1001,10 +996,10 @@
         <v>116</v>
       </c>
       <c r="S3">
-        <v>42.775862</v>
+        <v>42.775861999999996</v>
       </c>
       <c r="T3">
-        <v>2.72877</v>
+        <v>2.7287699999999999</v>
       </c>
       <c r="U3">
         <v>112</v>
@@ -1013,16 +1008,16 @@
         <v>2.634674</v>
       </c>
       <c r="W3">
-        <v>44.303571</v>
+        <v>44.303570999999998</v>
       </c>
       <c r="X3">
         <v>61</v>
       </c>
       <c r="Y3">
-        <v>81.344262</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
+        <v>81.344262000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1051,7 +1046,7 @@
         <v>1.29572</v>
       </c>
       <c r="J4">
-        <v>50.27272727</v>
+        <v>50.272727269999997</v>
       </c>
       <c r="K4">
         <v>160</v>
@@ -1075,16 +1070,16 @@
         <v>99</v>
       </c>
       <c r="S4">
-        <v>50.272727</v>
+        <v>50.272727000000003</v>
       </c>
       <c r="T4">
-        <v>1.858108</v>
+        <v>1.8581080000000001</v>
       </c>
       <c r="U4">
         <v>96</v>
       </c>
       <c r="V4">
-        <v>1.801802</v>
+        <v>1.8018019999999999</v>
       </c>
       <c r="W4">
         <v>51.84375</v>
@@ -1096,7 +1091,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -1122,10 +1117,10 @@
         <v>3854</v>
       </c>
       <c r="I5">
-        <v>1.414634</v>
+        <v>1.4146339999999999</v>
       </c>
       <c r="J5">
-        <v>38.66929134</v>
+        <v>38.669291340000001</v>
       </c>
       <c r="K5">
         <v>160</v>
@@ -1143,34 +1138,34 @@
         <v>5452</v>
       </c>
       <c r="P5">
-        <v>900.77036</v>
+        <v>900.77035999999998</v>
       </c>
       <c r="Q5">
         <v>127</v>
       </c>
       <c r="S5">
-        <v>38.669291</v>
+        <v>38.669291000000001</v>
       </c>
       <c r="T5">
-        <v>2.32942</v>
+        <v>2.3294199999999998</v>
       </c>
       <c r="U5">
         <v>141</v>
       </c>
       <c r="V5">
-        <v>2.586207</v>
+        <v>2.5862069999999999</v>
       </c>
       <c r="W5">
-        <v>34.829787</v>
+        <v>34.829787000000003</v>
       </c>
       <c r="X5">
         <v>79</v>
       </c>
       <c r="Y5">
-        <v>62.164557</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>62.164557000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -1199,7 +1194,7 @@
         <v>1.803299</v>
       </c>
       <c r="J6">
-        <v>49.18811881</v>
+        <v>49.188118809999999</v>
       </c>
       <c r="K6">
         <v>160</v>
@@ -1217,7 +1212,7 @@
         <v>5904</v>
       </c>
       <c r="P6">
-        <v>841.463415</v>
+        <v>841.46341500000005</v>
       </c>
       <c r="Q6">
         <v>101</v>
@@ -1226,25 +1221,25 @@
         <v>49.188119</v>
       </c>
       <c r="T6">
-        <v>1.710705</v>
+        <v>1.7107049999999999</v>
       </c>
       <c r="U6">
         <v>110</v>
       </c>
       <c r="V6">
-        <v>1.863144</v>
+        <v>1.8631439999999999</v>
       </c>
       <c r="W6">
-        <v>45.163636</v>
+        <v>45.163635999999997</v>
       </c>
       <c r="X6">
         <v>58</v>
       </c>
       <c r="Y6">
-        <v>85.655172</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+        <v>85.655171999999993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -1270,7 +1265,7 @@
         <v>3821</v>
       </c>
       <c r="I7">
-        <v>1.266161</v>
+        <v>1.2661610000000001</v>
       </c>
       <c r="J7">
         <v>24.32019704</v>
@@ -1300,25 +1295,25 @@
         <v>24.320197</v>
       </c>
       <c r="T7">
-        <v>4.195949</v>
+        <v>4.1959489999999997</v>
       </c>
       <c r="U7">
         <v>216</v>
       </c>
       <c r="V7">
-        <v>4.464655</v>
+        <v>4.4646549999999996</v>
       </c>
       <c r="W7">
-        <v>22.856481</v>
+        <v>22.856480999999999</v>
       </c>
       <c r="X7">
         <v>125</v>
       </c>
       <c r="Y7">
-        <v>39.496</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>39.496000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1347,7 +1342,7 @@
         <v>1.359693</v>
       </c>
       <c r="J8">
-        <v>30.49693252</v>
+        <v>30.496932520000001</v>
       </c>
       <c r="K8">
         <v>160</v>
@@ -1365,22 +1360,22 @@
         <v>5674</v>
       </c>
       <c r="P8">
-        <v>876.101516</v>
+        <v>876.10151599999995</v>
       </c>
       <c r="Q8">
         <v>163</v>
       </c>
       <c r="S8">
-        <v>30.496933</v>
+        <v>30.496932999999999</v>
       </c>
       <c r="T8">
-        <v>2.872753</v>
+        <v>2.8727529999999999</v>
       </c>
       <c r="U8">
         <v>178</v>
       </c>
       <c r="V8">
-        <v>3.137117</v>
+        <v>3.1371169999999999</v>
       </c>
       <c r="W8">
         <v>27.926966</v>
@@ -1389,10 +1384,10 @@
         <v>94</v>
       </c>
       <c r="Y8">
-        <v>52.882979</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+        <v>52.882978999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -1421,7 +1416,7 @@
         <v>1.224081</v>
       </c>
       <c r="J9">
-        <v>45.37272727</v>
+        <v>45.372727269999999</v>
       </c>
       <c r="K9" t="s">
         <v>42</v>
@@ -1439,34 +1434,34 @@
         <v>6730</v>
       </c>
       <c r="P9">
-        <v>741.604755</v>
+        <v>741.60475499999995</v>
       </c>
       <c r="Q9">
         <v>135</v>
       </c>
       <c r="S9">
-        <v>36.97037</v>
+        <v>36.970370000000003</v>
       </c>
       <c r="T9">
-        <v>2.005944</v>
+        <v>2.0059439999999999</v>
       </c>
       <c r="U9">
         <v>170</v>
       </c>
       <c r="V9">
-        <v>2.526003</v>
+        <v>2.5260030000000002</v>
       </c>
       <c r="W9">
-        <v>29.358824</v>
+        <v>29.358823999999998</v>
       </c>
       <c r="X9">
         <v>110</v>
       </c>
       <c r="Y9">
-        <v>45.372727</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>45.372726999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1516,7 +1511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -1542,10 +1537,10 @@
         <v>3702</v>
       </c>
       <c r="I11">
-        <v>1.41383</v>
+        <v>1.4138299999999999</v>
       </c>
       <c r="J11">
-        <v>55.72340426</v>
+        <v>55.723404260000002</v>
       </c>
       <c r="K11" t="s">
         <v>42</v>
@@ -1578,19 +1573,19 @@
         <v>115</v>
       </c>
       <c r="V11">
-        <v>2.197172</v>
+        <v>2.1971720000000001</v>
       </c>
       <c r="W11">
-        <v>45.547826</v>
+        <v>45.547826000000001</v>
       </c>
       <c r="X11">
         <v>94</v>
       </c>
       <c r="Y11">
-        <v>55.723404</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
+        <v>55.723404000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -1619,7 +1614,7 @@
         <v>1.215622</v>
       </c>
       <c r="J12">
-        <v>49.06306306</v>
+        <v>49.063063059999998</v>
       </c>
       <c r="K12" t="s">
         <v>42</v>
@@ -1637,7 +1632,7 @@
         <v>4420</v>
       </c>
       <c r="P12">
-        <v>1232.126697</v>
+        <v>1232.1266969999999</v>
       </c>
       <c r="Q12">
         <v>128</v>
@@ -1646,16 +1641,16 @@
         <v>42.546875</v>
       </c>
       <c r="T12">
-        <v>2.895928</v>
+        <v>2.8959280000000001</v>
       </c>
       <c r="U12">
         <v>135</v>
       </c>
       <c r="V12">
-        <v>3.054299</v>
+        <v>3.0542989999999999</v>
       </c>
       <c r="W12">
-        <v>40.340741</v>
+        <v>40.340741000000001</v>
       </c>
       <c r="X12">
         <v>111</v>
@@ -1664,7 +1659,7 @@
         <v>49.063063</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1690,10 +1685,10 @@
         <v>2678</v>
       </c>
       <c r="I13">
-        <v>1.087379</v>
+        <v>1.0873790000000001</v>
       </c>
       <c r="J13">
-        <v>63.70731707</v>
+        <v>63.707317070000002</v>
       </c>
       <c r="K13" t="s">
         <v>42</v>
@@ -1711,7 +1706,7 @@
         <v>2912</v>
       </c>
       <c r="P13">
-        <v>896.978022</v>
+        <v>896.97802200000001</v>
       </c>
       <c r="Q13">
         <v>50</v>
@@ -1735,10 +1730,10 @@
         <v>41</v>
       </c>
       <c r="Y13">
-        <v>63.707317</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
+        <v>63.707317000000003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1764,10 +1759,10 @@
         <v>3624</v>
       </c>
       <c r="I14">
-        <v>1.161976</v>
+        <v>1.1619759999999999</v>
       </c>
       <c r="J14">
-        <v>70.62820513</v>
+        <v>70.628205129999998</v>
       </c>
       <c r="K14" t="s">
         <v>42</v>
@@ -1791,16 +1786,16 @@
         <v>116</v>
       </c>
       <c r="S14">
-        <v>47.491379</v>
+        <v>47.491379000000002</v>
       </c>
       <c r="T14">
-        <v>2.75469</v>
+        <v>2.7546900000000001</v>
       </c>
       <c r="U14">
         <v>113</v>
       </c>
       <c r="V14">
-        <v>2.683448</v>
+        <v>2.6834479999999998</v>
       </c>
       <c r="W14">
         <v>48.752212</v>
@@ -1809,10 +1804,10 @@
         <v>78</v>
       </c>
       <c r="Y14">
-        <v>70.628205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+        <v>70.628204999999994</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1838,10 +1833,10 @@
         <v>3515</v>
       </c>
       <c r="I15">
-        <v>1.25889</v>
+        <v>1.2588900000000001</v>
       </c>
       <c r="J15">
-        <v>51.84158416</v>
+        <v>51.841584159999996</v>
       </c>
       <c r="K15" t="s">
         <v>42</v>
@@ -1865,16 +1860,16 @@
         <v>113</v>
       </c>
       <c r="S15">
-        <v>46.336283</v>
+        <v>46.336283000000002</v>
       </c>
       <c r="T15">
-        <v>2.553672</v>
+        <v>2.5536720000000002</v>
       </c>
       <c r="U15">
         <v>118</v>
       </c>
       <c r="V15">
-        <v>2.666667</v>
+        <v>2.6666669999999999</v>
       </c>
       <c r="W15">
         <v>44.372881</v>
@@ -1883,10 +1878,10 @@
         <v>101</v>
       </c>
       <c r="Y15">
-        <v>51.841584</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+        <v>51.841583999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1912,10 +1907,10 @@
         <v>4243</v>
       </c>
       <c r="I16">
-        <v>1.341268</v>
+        <v>1.3412679999999999</v>
       </c>
       <c r="J16">
-        <v>47.78571429</v>
+        <v>47.785714290000001</v>
       </c>
       <c r="K16" t="s">
         <v>42</v>
@@ -1933,7 +1928,7 @@
         <v>5691</v>
       </c>
       <c r="P16">
-        <v>940.432261</v>
+        <v>940.43226100000004</v>
       </c>
       <c r="Q16">
         <v>150</v>
@@ -1942,13 +1937,13 @@
         <v>35.68</v>
       </c>
       <c r="T16">
-        <v>2.635741</v>
+        <v>2.6357409999999999</v>
       </c>
       <c r="U16">
         <v>176</v>
       </c>
       <c r="V16">
-        <v>3.092602</v>
+        <v>3.0926019999999999</v>
       </c>
       <c r="W16">
         <v>30.409091</v>
@@ -1957,10 +1952,10 @@
         <v>112</v>
       </c>
       <c r="Y16">
-        <v>47.785714</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+        <v>47.785713999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1989,7 +1984,7 @@
         <v>1.397235</v>
       </c>
       <c r="J17">
-        <v>44.31404959</v>
+        <v>44.314049590000003</v>
       </c>
       <c r="K17" t="s">
         <v>42</v>
@@ -2007,7 +2002,7 @@
         <v>6064</v>
       </c>
       <c r="P17">
-        <v>884.234829</v>
+        <v>884.23482899999999</v>
       </c>
       <c r="Q17">
         <v>158</v>
@@ -2016,25 +2011,25 @@
         <v>33.936709</v>
       </c>
       <c r="T17">
-        <v>2.605541</v>
+        <v>2.6055410000000001</v>
       </c>
       <c r="U17">
         <v>182</v>
       </c>
       <c r="V17">
-        <v>3.001319</v>
+        <v>3.0013190000000001</v>
       </c>
       <c r="W17">
-        <v>29.461538</v>
+        <v>29.461538000000001</v>
       </c>
       <c r="X17">
         <v>121</v>
       </c>
       <c r="Y17">
-        <v>44.31405</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>44.314050000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -2063,7 +2058,7 @@
         <v>1.320997</v>
       </c>
       <c r="J18">
-        <v>67.23170732</v>
+        <v>67.231707319999998</v>
       </c>
       <c r="K18" t="s">
         <v>42</v>
@@ -2087,16 +2082,16 @@
         <v>111</v>
       </c>
       <c r="S18">
-        <v>49.666667</v>
+        <v>49.666666999999997</v>
       </c>
       <c r="T18">
-        <v>2.073216</v>
+        <v>2.0732159999999999</v>
       </c>
       <c r="U18">
         <v>126</v>
       </c>
       <c r="V18">
-        <v>2.353381</v>
+        <v>2.3533810000000002</v>
       </c>
       <c r="W18">
         <v>43.753968</v>
@@ -2108,7 +2103,7 @@
         <v>67.231707</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -2134,10 +2129,10 @@
         <v>2780</v>
       </c>
       <c r="I19">
-        <v>1.797122</v>
+        <v>1.7971220000000001</v>
       </c>
       <c r="J19">
-        <v>99.11111111</v>
+        <v>99.111111109999996</v>
       </c>
       <c r="K19" t="s">
         <v>42</v>
@@ -2161,28 +2156,28 @@
         <v>72</v>
       </c>
       <c r="S19">
-        <v>74.333333</v>
+        <v>74.333332999999996</v>
       </c>
       <c r="T19">
-        <v>1.441153</v>
+        <v>1.4411529999999999</v>
       </c>
       <c r="U19">
         <v>83</v>
       </c>
       <c r="V19">
-        <v>1.661329</v>
+        <v>1.6613290000000001</v>
       </c>
       <c r="W19">
-        <v>64.481928</v>
+        <v>64.481927999999996</v>
       </c>
       <c r="X19">
         <v>54</v>
       </c>
       <c r="Y19">
-        <v>99.111111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25">
+        <v>99.111110999999994</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -2211,7 +2206,7 @@
         <v>1.595882</v>
       </c>
       <c r="J20">
-        <v>75.05479452</v>
+        <v>75.054794520000002</v>
       </c>
       <c r="K20" t="s">
         <v>42</v>
@@ -2244,7 +2239,7 @@
         <v>100</v>
       </c>
       <c r="V20">
-        <v>2.016129</v>
+        <v>2.0161289999999998</v>
       </c>
       <c r="W20">
         <v>54.79</v>
@@ -2253,10 +2248,10 @@
         <v>73</v>
       </c>
       <c r="Y20">
-        <v>75.054795</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
+        <v>75.054794999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -2285,7 +2280,7 @@
         <v>1.190607</v>
       </c>
       <c r="J21">
-        <v>44.59689922</v>
+        <v>44.596899219999997</v>
       </c>
       <c r="K21" t="s">
         <v>42</v>
@@ -2303,13 +2298,13 @@
         <v>3473</v>
       </c>
       <c r="P21">
-        <v>1656.492946</v>
+        <v>1656.4929460000001</v>
       </c>
       <c r="Q21">
         <v>152</v>
       </c>
       <c r="S21">
-        <v>37.848684</v>
+        <v>37.848683999999999</v>
       </c>
       <c r="T21">
         <v>4.37662</v>
@@ -2318,19 +2313,19 @@
         <v>171</v>
       </c>
       <c r="V21">
-        <v>4.923697</v>
+        <v>4.9236969999999998</v>
       </c>
       <c r="W21">
-        <v>33.643275</v>
+        <v>33.643275000000003</v>
       </c>
       <c r="X21">
         <v>129</v>
       </c>
       <c r="Y21">
-        <v>44.596899</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+        <v>44.596899000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -2359,7 +2354,7 @@
         <v>1.804422</v>
       </c>
       <c r="J22">
-        <v>64.10588235</v>
+        <v>64.105882350000002</v>
       </c>
       <c r="K22" t="s">
         <v>42</v>
@@ -2377,7 +2372,7 @@
         <v>5794</v>
       </c>
       <c r="P22">
-        <v>940.455644</v>
+        <v>940.45564400000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -2386,25 +2381,25 @@
         <v>54.49</v>
       </c>
       <c r="T22">
-        <v>1.725923</v>
+        <v>1.7259230000000001</v>
       </c>
       <c r="U22">
         <v>113</v>
       </c>
       <c r="V22">
-        <v>1.950293</v>
+        <v>1.9502930000000001</v>
       </c>
       <c r="W22">
-        <v>48.221239</v>
+        <v>48.221238999999997</v>
       </c>
       <c r="X22">
         <v>85</v>
       </c>
       <c r="Y22">
-        <v>64.105882</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25">
+        <v>64.105881999999994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2430,7 +2425,7 @@
         <v>4173</v>
       </c>
       <c r="I23">
-        <v>1.430386</v>
+        <v>1.4303859999999999</v>
       </c>
       <c r="J23">
         <v>65.52873563</v>
@@ -2451,7 +2446,7 @@
         <v>5969</v>
       </c>
       <c r="P23">
-        <v>955.101357</v>
+        <v>955.10135700000001</v>
       </c>
       <c r="Q23">
         <v>126</v>
@@ -2460,25 +2455,25 @@
         <v>45.246032</v>
       </c>
       <c r="T23">
-        <v>2.110906</v>
+        <v>2.1109059999999999</v>
       </c>
       <c r="U23">
         <v>154</v>
       </c>
       <c r="V23">
-        <v>2.579997</v>
+        <v>2.5799970000000001</v>
       </c>
       <c r="W23">
-        <v>37.019481</v>
+        <v>37.019480999999999</v>
       </c>
       <c r="X23">
         <v>87</v>
       </c>
       <c r="Y23">
-        <v>65.528736</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25">
+        <v>65.528735999999995</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2504,10 +2499,10 @@
         <v>4694</v>
       </c>
       <c r="I24">
-        <v>1.250746</v>
+        <v>1.2507459999999999</v>
       </c>
       <c r="J24">
-        <v>58.21359223</v>
+        <v>58.213592230000003</v>
       </c>
       <c r="K24" t="s">
         <v>42</v>
@@ -2534,25 +2529,25 @@
         <v>45.424242</v>
       </c>
       <c r="T24">
-        <v>2.248339</v>
+        <v>2.2483390000000001</v>
       </c>
       <c r="U24">
         <v>163</v>
       </c>
       <c r="V24">
-        <v>2.776358</v>
+        <v>2.7763580000000001</v>
       </c>
       <c r="W24">
-        <v>36.785276</v>
+        <v>36.785276000000003</v>
       </c>
       <c r="X24">
         <v>103</v>
       </c>
       <c r="Y24">
-        <v>58.213592</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
+        <v>58.213591999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2578,10 +2573,10 @@
         <v>5073</v>
       </c>
       <c r="I25">
-        <v>1.38084</v>
+        <v>1.3808400000000001</v>
       </c>
       <c r="J25">
-        <v>26.80952381</v>
+        <v>26.809523810000002</v>
       </c>
       <c r="K25" t="s">
         <v>42</v>
@@ -2605,19 +2600,19 @@
         <v>252</v>
       </c>
       <c r="S25">
-        <v>22.34127</v>
+        <v>22.341270000000002</v>
       </c>
       <c r="T25">
-        <v>3.59743</v>
+        <v>3.5974300000000001</v>
       </c>
       <c r="U25">
         <v>282</v>
       </c>
       <c r="V25">
-        <v>4.025696</v>
+        <v>4.0256959999999999</v>
       </c>
       <c r="W25">
-        <v>19.964539</v>
+        <v>19.964538999999998</v>
       </c>
       <c r="X25">
         <v>210</v>
@@ -2626,7 +2621,7 @@
         <v>26.809524</v>
       </c>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>25</v>
       </c>
@@ -2652,10 +2647,10 @@
         <v>4039</v>
       </c>
       <c r="I26">
-        <v>1.272345</v>
+        <v>1.2723450000000001</v>
       </c>
       <c r="J26">
-        <v>45.35074627</v>
+        <v>45.350746270000002</v>
       </c>
       <c r="K26" t="s">
         <v>42</v>
@@ -2679,7 +2674,7 @@
         <v>139</v>
       </c>
       <c r="S26">
-        <v>43.719424</v>
+        <v>43.719423999999997</v>
       </c>
       <c r="T26">
         <v>2.704806</v>
@@ -2697,10 +2692,10 @@
         <v>134</v>
       </c>
       <c r="Y26">
-        <v>45.350746</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25">
+        <v>45.350746000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>25</v>
       </c>
@@ -2726,10 +2721,10 @@
         <v>7128</v>
       </c>
       <c r="I27">
-        <v>1.28353</v>
+        <v>1.2835300000000001</v>
       </c>
       <c r="J27">
-        <v>15.76231884</v>
+        <v>15.762318840000001</v>
       </c>
       <c r="K27" t="s">
         <v>42</v>
@@ -2747,25 +2742,25 @@
         <v>9149</v>
       </c>
       <c r="P27">
-        <v>594.3819</v>
+        <v>594.38189999999997</v>
       </c>
       <c r="Q27">
         <v>460</v>
       </c>
       <c r="S27">
-        <v>11.821739</v>
+        <v>11.821739000000001</v>
       </c>
       <c r="T27">
-        <v>5.027872</v>
+        <v>5.0278720000000003</v>
       </c>
       <c r="U27">
         <v>597</v>
       </c>
       <c r="V27">
-        <v>6.525303</v>
+        <v>6.5253030000000001</v>
       </c>
       <c r="W27">
-        <v>9.108878</v>
+        <v>9.1088780000000007</v>
       </c>
       <c r="X27">
         <v>345</v>
@@ -2774,7 +2769,7 @@
         <v>15.762319</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -2800,7 +2795,7 @@
         <v>3036</v>
       </c>
       <c r="I28">
-        <v>1.629117</v>
+        <v>1.6291169999999999</v>
       </c>
       <c r="J28">
         <v>60.94897959</v>
@@ -2821,34 +2816,34 @@
         <v>4946</v>
       </c>
       <c r="P28">
-        <v>1207.642539</v>
+        <v>1207.6425389999999</v>
       </c>
       <c r="Q28">
         <v>119</v>
       </c>
       <c r="S28">
-        <v>50.193277</v>
+        <v>50.193277000000002</v>
       </c>
       <c r="T28">
-        <v>2.405985</v>
+        <v>2.4059849999999998</v>
       </c>
       <c r="U28">
         <v>126</v>
       </c>
       <c r="V28">
-        <v>2.547513</v>
+        <v>2.5475129999999999</v>
       </c>
       <c r="W28">
-        <v>47.404762</v>
+        <v>47.404761999999998</v>
       </c>
       <c r="X28">
         <v>98</v>
       </c>
       <c r="Y28">
-        <v>60.94898</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25">
+        <v>60.948979999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>25</v>
       </c>
@@ -2874,7 +2869,7 @@
         <v>3340</v>
       </c>
       <c r="I29">
-        <v>1.493114</v>
+        <v>1.4931140000000001</v>
       </c>
       <c r="J29">
         <v>51.984375</v>
@@ -2901,19 +2896,19 @@
         <v>137</v>
       </c>
       <c r="S29">
-        <v>48.569343</v>
+        <v>48.569343000000003</v>
       </c>
       <c r="T29">
-        <v>2.747143</v>
+        <v>2.7471429999999999</v>
       </c>
       <c r="U29">
         <v>147</v>
       </c>
       <c r="V29">
-        <v>2.947664</v>
+        <v>2.9476640000000001</v>
       </c>
       <c r="W29">
-        <v>45.265306</v>
+        <v>45.265306000000002</v>
       </c>
       <c r="X29">
         <v>128</v>
@@ -2922,7 +2917,7 @@
         <v>51.984375</v>
       </c>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -2951,7 +2946,7 @@
         <v>1.513609</v>
       </c>
       <c r="J30">
-        <v>77.48051948</v>
+        <v>77.480519479999998</v>
       </c>
       <c r="K30" t="s">
         <v>42</v>
@@ -2969,13 +2964,13 @@
         <v>6006</v>
       </c>
       <c r="P30">
-        <v>993.339993</v>
+        <v>993.33999300000005</v>
       </c>
       <c r="Q30">
         <v>89</v>
       </c>
       <c r="S30">
-        <v>67.033708</v>
+        <v>67.033708000000004</v>
       </c>
       <c r="T30">
         <v>1.481851</v>
@@ -2984,19 +2979,19 @@
         <v>104</v>
       </c>
       <c r="V30">
-        <v>1.731602</v>
+        <v>1.7316020000000001</v>
       </c>
       <c r="W30">
-        <v>57.365385</v>
+        <v>57.365385000000003</v>
       </c>
       <c r="X30">
         <v>77</v>
       </c>
       <c r="Y30">
-        <v>77.480519</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25">
+        <v>77.480519000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>25</v>
       </c>
@@ -3022,10 +3017,10 @@
         <v>4754</v>
       </c>
       <c r="I31">
-        <v>1.286706</v>
+        <v>1.2867059999999999</v>
       </c>
       <c r="J31">
-        <v>73.425</v>
+        <v>73.424999999999997</v>
       </c>
       <c r="K31" t="s">
         <v>42</v>
@@ -3043,13 +3038,13 @@
         <v>6117</v>
       </c>
       <c r="P31">
-        <v>960.274644</v>
+        <v>960.27464399999997</v>
       </c>
       <c r="Q31">
         <v>114</v>
       </c>
       <c r="S31">
-        <v>51.526316</v>
+        <v>51.526316000000001</v>
       </c>
       <c r="T31">
         <v>1.863659</v>
@@ -3058,19 +3053,19 @@
         <v>163</v>
       </c>
       <c r="V31">
-        <v>2.664705</v>
+        <v>2.6647050000000001</v>
       </c>
       <c r="W31">
-        <v>36.03681</v>
+        <v>36.036810000000003</v>
       </c>
       <c r="X31">
         <v>80</v>
       </c>
       <c r="Y31">
-        <v>73.425</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25">
+        <v>73.424999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -3096,10 +3091,10 @@
         <v>5561</v>
       </c>
       <c r="I32">
-        <v>1.24528</v>
+        <v>1.2452799999999999</v>
       </c>
       <c r="J32">
-        <v>72.02325581</v>
+        <v>72.023255809999995</v>
       </c>
       <c r="K32" t="s">
         <v>42</v>
@@ -3117,16 +3112,16 @@
         <v>6925</v>
       </c>
       <c r="P32">
-        <v>894.440433</v>
+        <v>894.44043299999998</v>
       </c>
       <c r="Q32">
         <v>105</v>
       </c>
       <c r="S32">
-        <v>58.990476</v>
+        <v>58.990476000000001</v>
       </c>
       <c r="T32">
-        <v>1.516245</v>
+        <v>1.5162450000000001</v>
       </c>
       <c r="U32">
         <v>113</v>
@@ -3135,16 +3130,16 @@
         <v>1.631769</v>
       </c>
       <c r="W32">
-        <v>54.814159</v>
+        <v>54.814158999999997</v>
       </c>
       <c r="X32">
         <v>86</v>
       </c>
       <c r="Y32">
-        <v>72.023256</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25">
+        <v>72.023256000000003</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -3173,7 +3168,7 @@
         <v>1.485714</v>
       </c>
       <c r="J33">
-        <v>66.34408602</v>
+        <v>66.344086020000006</v>
       </c>
       <c r="K33" t="s">
         <v>42</v>
@@ -3197,7 +3192,7 @@
         <v>106</v>
       </c>
       <c r="S33">
-        <v>58.207547</v>
+        <v>58.207546999999998</v>
       </c>
       <c r="T33">
         <v>1.820055</v>
@@ -3206,19 +3201,19 @@
         <v>120</v>
       </c>
       <c r="V33">
-        <v>2.06044</v>
+        <v>2.0604399999999998</v>
       </c>
       <c r="W33">
-        <v>51.416667</v>
+        <v>51.416666999999997</v>
       </c>
       <c r="X33">
         <v>93</v>
       </c>
       <c r="Y33">
-        <v>66.344086</v>
-      </c>
-    </row>
-    <row r="34" spans="1:25">
+        <v>66.344086000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -3244,10 +3239,10 @@
         <v>4061</v>
       </c>
       <c r="I34">
-        <v>1.312731</v>
+        <v>1.3127310000000001</v>
       </c>
       <c r="J34">
-        <v>69.52747253</v>
+        <v>69.527472529999997</v>
       </c>
       <c r="K34" t="s">
         <v>42</v>
@@ -3271,16 +3266,16 @@
         <v>105</v>
       </c>
       <c r="S34">
-        <v>60.257143</v>
+        <v>60.257142999999999</v>
       </c>
       <c r="T34">
-        <v>1.969612</v>
+        <v>1.9696119999999999</v>
       </c>
       <c r="U34">
         <v>129</v>
       </c>
       <c r="V34">
-        <v>2.419809</v>
+        <v>2.4198089999999999</v>
       </c>
       <c r="W34">
         <v>49.046512</v>
@@ -3289,10 +3284,10 @@
         <v>91</v>
       </c>
       <c r="Y34">
-        <v>69.527473</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25">
+        <v>69.527473000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -3339,16 +3334,16 @@
         <v>6990</v>
       </c>
       <c r="P35">
-        <v>814.592275</v>
+        <v>814.59227499999997</v>
       </c>
       <c r="Q35">
         <v>242</v>
       </c>
       <c r="S35">
-        <v>23.528926</v>
+        <v>23.528925999999998</v>
       </c>
       <c r="T35">
-        <v>3.462089</v>
+        <v>3.4620890000000002</v>
       </c>
       <c r="U35">
         <v>272</v>
@@ -3357,16 +3352,16 @@
         <v>3.891273</v>
       </c>
       <c r="W35">
-        <v>20.933824</v>
+        <v>20.933824000000001</v>
       </c>
       <c r="X35">
         <v>190</v>
       </c>
       <c r="Y35">
-        <v>29.968421</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25">
+        <v>29.968420999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -3392,10 +3387,10 @@
         <v>3407</v>
       </c>
       <c r="I36">
-        <v>1.549457</v>
+        <v>1.5494570000000001</v>
       </c>
       <c r="J36">
-        <v>57.73255814</v>
+        <v>57.732558140000002</v>
       </c>
       <c r="K36" t="s">
         <v>42</v>
@@ -3413,13 +3408,13 @@
         <v>5279</v>
       </c>
       <c r="P36">
-        <v>940.519038</v>
+        <v>940.51903800000002</v>
       </c>
       <c r="Q36">
         <v>104</v>
       </c>
       <c r="S36">
-        <v>47.740385</v>
+        <v>47.740385000000003</v>
       </c>
       <c r="T36">
         <v>1.97007</v>
@@ -3428,19 +3423,19 @@
         <v>119</v>
       </c>
       <c r="V36">
-        <v>2.254215</v>
+        <v>2.2542149999999999</v>
       </c>
       <c r="W36">
-        <v>41.722689</v>
+        <v>41.722689000000003</v>
       </c>
       <c r="X36">
         <v>86</v>
       </c>
       <c r="Y36">
-        <v>57.732558</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25">
+        <v>57.732557999999997</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -3466,10 +3461,10 @@
         <v>5470</v>
       </c>
       <c r="I37">
-        <v>1.291956</v>
+        <v>1.2919560000000001</v>
       </c>
       <c r="J37">
-        <v>30.48447205</v>
+        <v>30.484472050000001</v>
       </c>
       <c r="K37" t="s">
         <v>42</v>
@@ -3493,7 +3488,7 @@
         <v>179</v>
       </c>
       <c r="S37">
-        <v>27.418994</v>
+        <v>27.418994000000001</v>
       </c>
       <c r="T37">
         <v>2.532899</v>
@@ -3502,10 +3497,10 @@
         <v>186</v>
       </c>
       <c r="V37">
-        <v>2.631951</v>
+        <v>2.6319509999999999</v>
       </c>
       <c r="W37">
-        <v>26.387097</v>
+        <v>26.387097000000001</v>
       </c>
       <c r="X37">
         <v>161</v>
@@ -3514,7 +3509,7 @@
         <v>30.484472</v>
       </c>
     </row>
-    <row r="38" spans="1:25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -3540,7 +3535,7 @@
         <v>3764</v>
       </c>
       <c r="I38">
-        <v>1.190489</v>
+        <v>1.1904889999999999</v>
       </c>
       <c r="J38">
         <v>63.53846154</v>
@@ -3561,13 +3556,13 @@
         <v>4481</v>
       </c>
       <c r="P38">
-        <v>1106.003124</v>
+        <v>1106.0031240000001</v>
       </c>
       <c r="Q38">
         <v>103</v>
       </c>
       <c r="S38">
-        <v>48.116505</v>
+        <v>48.116504999999997</v>
       </c>
       <c r="T38">
         <v>2.298594</v>
@@ -3579,16 +3574,16 @@
         <v>2.588708</v>
       </c>
       <c r="W38">
-        <v>42.724138</v>
+        <v>42.724138000000004</v>
       </c>
       <c r="X38">
         <v>78</v>
       </c>
       <c r="Y38">
-        <v>63.538462</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25">
+        <v>63.538462000000003</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -3614,10 +3609,10 @@
         <v>4626</v>
       </c>
       <c r="I39">
-        <v>1.366191</v>
+        <v>1.3661909999999999</v>
       </c>
       <c r="J39">
-        <v>56.14606742</v>
+        <v>56.146067420000001</v>
       </c>
       <c r="K39" t="s">
         <v>42</v>
@@ -3635,16 +3630,16 @@
         <v>6320</v>
       </c>
       <c r="P39">
-        <v>790.664557</v>
+        <v>790.66455699999995</v>
       </c>
       <c r="Q39">
         <v>129</v>
       </c>
       <c r="S39">
-        <v>38.736434</v>
+        <v>38.736434000000003</v>
       </c>
       <c r="T39">
-        <v>2.041139</v>
+        <v>2.0411389999999998</v>
       </c>
       <c r="U39">
         <v>162</v>
@@ -3653,16 +3648,16 @@
         <v>2.563291</v>
       </c>
       <c r="W39">
-        <v>30.845679</v>
+        <v>30.845679000000001</v>
       </c>
       <c r="X39">
         <v>89</v>
       </c>
       <c r="Y39">
-        <v>56.146067</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25">
+        <v>56.146067000000002</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>25</v>
       </c>
@@ -3691,7 +3686,7 @@
         <v>1.237514</v>
       </c>
       <c r="J40">
-        <v>52.96808511</v>
+        <v>52.968085109999997</v>
       </c>
       <c r="K40" t="s">
         <v>42</v>
@@ -3709,16 +3704,16 @@
         <v>5575</v>
       </c>
       <c r="P40">
-        <v>893.09417</v>
+        <v>893.09416999999996</v>
       </c>
       <c r="Q40">
         <v>113</v>
       </c>
       <c r="S40">
-        <v>44.061947</v>
+        <v>44.061947000000004</v>
       </c>
       <c r="T40">
-        <v>2.026906</v>
+        <v>2.0269059999999999</v>
       </c>
       <c r="U40">
         <v>129</v>
@@ -3727,16 +3722,16 @@
         <v>2.313901</v>
       </c>
       <c r="W40">
-        <v>38.596899</v>
+        <v>38.596899000000001</v>
       </c>
       <c r="X40">
         <v>94</v>
       </c>
       <c r="Y40">
-        <v>52.968085</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25">
+        <v>52.968085000000002</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -3762,10 +3757,10 @@
         <v>4597</v>
       </c>
       <c r="I41">
-        <v>1.397868</v>
+        <v>1.3978680000000001</v>
       </c>
       <c r="J41">
-        <v>21.11297071</v>
+        <v>21.112970709999999</v>
       </c>
       <c r="K41" t="s">
         <v>42</v>
@@ -3789,16 +3784,16 @@
         <v>292</v>
       </c>
       <c r="S41">
-        <v>17.280822</v>
+        <v>17.280822000000001</v>
       </c>
       <c r="T41">
-        <v>4.54404</v>
+        <v>4.5440399999999999</v>
       </c>
       <c r="U41">
         <v>341</v>
       </c>
       <c r="V41">
-        <v>5.306567</v>
+        <v>5.3065670000000003</v>
       </c>
       <c r="W41">
         <v>14.797654</v>
@@ -3807,10 +3802,10 @@
         <v>239</v>
       </c>
       <c r="Y41">
-        <v>21.112971</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25">
+        <v>21.112971000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>25</v>
       </c>
@@ -3839,7 +3834,7 @@
         <v>1.459489</v>
       </c>
       <c r="J42">
-        <v>46.61111111</v>
+        <v>46.611111110000003</v>
       </c>
       <c r="K42" t="s">
         <v>42</v>
@@ -3857,22 +3852,22 @@
         <v>6737</v>
       </c>
       <c r="P42">
-        <v>747.216862</v>
+        <v>747.21686199999999</v>
       </c>
       <c r="Q42">
         <v>130</v>
       </c>
       <c r="S42">
-        <v>38.723077</v>
+        <v>38.723077000000004</v>
       </c>
       <c r="T42">
-        <v>1.929642</v>
+        <v>1.9296420000000001</v>
       </c>
       <c r="U42">
         <v>163</v>
       </c>
       <c r="V42">
-        <v>2.419475</v>
+        <v>2.4194749999999998</v>
       </c>
       <c r="W42">
         <v>30.883436</v>
@@ -3881,10 +3876,10 @@
         <v>108</v>
       </c>
       <c r="Y42">
-        <v>46.611111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25">
+        <v>46.611111000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>25</v>
       </c>
@@ -3910,10 +3905,10 @@
         <v>4075</v>
       </c>
       <c r="I43">
-        <v>1.297178</v>
+        <v>1.2971779999999999</v>
       </c>
       <c r="J43">
-        <v>57.90697674</v>
+        <v>57.906976739999998</v>
       </c>
       <c r="K43" t="s">
         <v>42</v>
@@ -3931,22 +3926,22 @@
         <v>5286</v>
       </c>
       <c r="P43">
-        <v>942.111237</v>
+        <v>942.11123699999996</v>
       </c>
       <c r="Q43">
         <v>98</v>
       </c>
       <c r="S43">
-        <v>50.816327</v>
+        <v>50.816327000000001</v>
       </c>
       <c r="T43">
-        <v>1.853954</v>
+        <v>1.8539540000000001</v>
       </c>
       <c r="U43">
         <v>120</v>
       </c>
       <c r="V43">
-        <v>2.270148</v>
+        <v>2.2701479999999998</v>
       </c>
       <c r="W43">
         <v>41.5</v>
@@ -3955,10 +3950,10 @@
         <v>86</v>
       </c>
       <c r="Y43">
-        <v>57.906977</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25">
+        <v>57.906976999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>25</v>
       </c>
@@ -4008,7 +4003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>25</v>
       </c>
@@ -4037,7 +4032,7 @@
         <v>1.441441</v>
       </c>
       <c r="J45">
-        <v>45.16964286</v>
+        <v>45.169642860000003</v>
       </c>
       <c r="K45" t="s">
         <v>42</v>
@@ -4055,7 +4050,7 @@
         <v>5760</v>
       </c>
       <c r="P45">
-        <v>878.298611</v>
+        <v>878.29861100000005</v>
       </c>
       <c r="Q45">
         <v>140</v>
@@ -4064,25 +4059,25 @@
         <v>36.135714</v>
       </c>
       <c r="T45">
-        <v>2.430556</v>
+        <v>2.4305560000000002</v>
       </c>
       <c r="U45">
         <v>164</v>
       </c>
       <c r="V45">
-        <v>2.847222</v>
+        <v>2.8472219999999999</v>
       </c>
       <c r="W45">
-        <v>30.847561</v>
+        <v>30.847560999999999</v>
       </c>
       <c r="X45">
         <v>112</v>
       </c>
       <c r="Y45">
-        <v>45.169643</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25">
+        <v>45.169643000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>25</v>
       </c>
@@ -4111,7 +4106,7 @@
         <v>1.403581</v>
       </c>
       <c r="J46">
-        <v>33.85234899</v>
+        <v>33.852348990000003</v>
       </c>
       <c r="K46" t="s">
         <v>42</v>
@@ -4129,22 +4124,22 @@
         <v>3763</v>
       </c>
       <c r="P46">
-        <v>1340.419878</v>
+        <v>1340.4198779999999</v>
       </c>
       <c r="Q46">
         <v>173</v>
       </c>
       <c r="S46">
-        <v>29.156069</v>
+        <v>29.156068999999999</v>
       </c>
       <c r="T46">
-        <v>4.597396</v>
+        <v>4.5973959999999998</v>
       </c>
       <c r="U46">
         <v>192</v>
       </c>
       <c r="V46">
-        <v>5.102312</v>
+        <v>5.1023120000000004</v>
       </c>
       <c r="W46">
         <v>26.270833</v>
@@ -4153,10 +4148,10 @@
         <v>149</v>
       </c>
       <c r="Y46">
-        <v>33.852349</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25">
+        <v>33.852348999999997</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>25</v>
       </c>
@@ -4182,10 +4177,10 @@
         <v>2294</v>
       </c>
       <c r="I47">
-        <v>1.352659</v>
+        <v>1.3526590000000001</v>
       </c>
       <c r="J47">
-        <v>56.83146067</v>
+        <v>56.831460669999998</v>
       </c>
       <c r="K47" t="s">
         <v>42</v>
@@ -4203,7 +4198,7 @@
         <v>3103</v>
       </c>
       <c r="P47">
-        <v>1630.03545</v>
+        <v>1630.0354500000001</v>
       </c>
       <c r="Q47">
         <v>100</v>
@@ -4212,25 +4207,25 @@
         <v>50.58</v>
       </c>
       <c r="T47">
-        <v>3.222688</v>
+        <v>3.2226880000000002</v>
       </c>
       <c r="U47">
         <v>104</v>
       </c>
       <c r="V47">
-        <v>3.351595</v>
+        <v>3.3515950000000001</v>
       </c>
       <c r="W47">
-        <v>48.634615</v>
+        <v>48.634614999999997</v>
       </c>
       <c r="X47">
         <v>89</v>
       </c>
       <c r="Y47">
-        <v>56.831461</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25">
+        <v>56.831460999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>25</v>
       </c>
@@ -4259,7 +4254,7 @@
         <v>1.332362</v>
       </c>
       <c r="J48">
-        <v>22.07423581</v>
+        <v>22.074235810000001</v>
       </c>
       <c r="K48" t="s">
         <v>42</v>
@@ -4277,34 +4272,34 @@
         <v>5031</v>
       </c>
       <c r="P48">
-        <v>1004.770423</v>
+        <v>1004.7704230000001</v>
       </c>
       <c r="Q48">
         <v>258</v>
       </c>
       <c r="S48">
-        <v>19.593023</v>
+        <v>19.593022999999999</v>
       </c>
       <c r="T48">
-        <v>5.128205</v>
+        <v>5.1282050000000003</v>
       </c>
       <c r="U48">
         <v>299</v>
       </c>
       <c r="V48">
-        <v>5.943152</v>
+        <v>5.9431520000000004</v>
       </c>
       <c r="W48">
-        <v>16.906355</v>
+        <v>16.906355000000001</v>
       </c>
       <c r="X48">
         <v>229</v>
       </c>
       <c r="Y48">
-        <v>22.074236</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25">
+        <v>22.074235999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>25</v>
       </c>
@@ -4333,7 +4328,7 @@
         <v>1.293166</v>
       </c>
       <c r="J49">
-        <v>64.16666667</v>
+        <v>64.166666669999998</v>
       </c>
       <c r="K49" t="s">
         <v>42</v>
@@ -4351,7 +4346,7 @@
         <v>7834</v>
       </c>
       <c r="P49">
-        <v>638.881797</v>
+        <v>638.88179700000001</v>
       </c>
       <c r="Q49">
         <v>88</v>
@@ -4360,13 +4355,13 @@
         <v>56.875</v>
       </c>
       <c r="T49">
-        <v>1.123309</v>
+        <v>1.1233089999999999</v>
       </c>
       <c r="U49">
         <v>103</v>
       </c>
       <c r="V49">
-        <v>1.314782</v>
+        <v>1.3147819999999999</v>
       </c>
       <c r="W49">
         <v>48.592233</v>
@@ -4375,10 +4370,10 @@
         <v>78</v>
       </c>
       <c r="Y49">
-        <v>64.166667</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25">
+        <v>64.166667000000004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>25</v>
       </c>
@@ -4404,7 +4399,7 @@
         <v>4848</v>
       </c>
       <c r="I50">
-        <v>2.705239</v>
+        <v>2.7052390000000002</v>
       </c>
       <c r="J50">
         <v>113.72727273</v>
@@ -4425,13 +4420,13 @@
         <v>13115</v>
       </c>
       <c r="P50">
-        <v>763.095692</v>
+        <v>763.09569199999999</v>
       </c>
       <c r="Q50">
         <v>141</v>
       </c>
       <c r="S50">
-        <v>70.978723</v>
+        <v>70.978723000000002</v>
       </c>
       <c r="T50">
         <v>1.075105</v>
@@ -4443,7 +4438,7 @@
         <v>1.181853</v>
       </c>
       <c r="W50">
-        <v>64.567742</v>
+        <v>64.567741999999996</v>
       </c>
       <c r="X50">
         <v>88</v>
@@ -4452,7 +4447,7 @@
         <v>113.727273</v>
       </c>
     </row>
-    <row r="51" spans="1:25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>25</v>
       </c>
@@ -4481,7 +4476,7 @@
         <v>1.269919</v>
       </c>
       <c r="J51">
-        <v>65.65789474</v>
+        <v>65.657894740000003</v>
       </c>
       <c r="K51" t="s">
         <v>42</v>
@@ -4499,16 +4494,16 @@
         <v>2343</v>
       </c>
       <c r="P51">
-        <v>1064.874093</v>
+        <v>1064.8740929999999</v>
       </c>
       <c r="Q51">
         <v>47</v>
       </c>
       <c r="S51">
-        <v>53.085106</v>
+        <v>53.085106000000003</v>
       </c>
       <c r="T51">
-        <v>2.005975</v>
+        <v>2.0059749999999998</v>
       </c>
       <c r="U51">
         <v>60</v>
@@ -4517,16 +4512,16 @@
         <v>2.560819</v>
       </c>
       <c r="W51">
-        <v>41.583333</v>
+        <v>41.583333000000003</v>
       </c>
       <c r="X51">
         <v>38</v>
       </c>
       <c r="Y51">
-        <v>65.657895</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25">
+        <v>65.657894999999996</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>25</v>
       </c>
@@ -4576,7 +4571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -4626,7 +4621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -4676,7 +4671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -4726,7 +4721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -4752,10 +4747,10 @@
         <v>6007</v>
       </c>
       <c r="I56">
-        <v>1.574996</v>
+        <v>1.5749960000000001</v>
       </c>
       <c r="J56">
-        <v>82.52892562</v>
+        <v>82.528925619999995</v>
       </c>
       <c r="K56" t="s">
         <v>42</v>
@@ -4779,7 +4774,7 @@
         <v>177</v>
       </c>
       <c r="S56">
-        <v>56.418079</v>
+        <v>56.418078999999999</v>
       </c>
       <c r="T56">
         <v>1.870838</v>
@@ -4791,16 +4786,16 @@
         <v>2.071663</v>
       </c>
       <c r="W56">
-        <v>50.94898</v>
+        <v>50.948979999999999</v>
       </c>
       <c r="X56">
         <v>121</v>
       </c>
       <c r="Y56">
-        <v>82.528926</v>
-      </c>
-    </row>
-    <row r="57" spans="1:25">
+        <v>82.528925999999998</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -4853,19 +4848,19 @@
         <v>276</v>
       </c>
       <c r="S57">
-        <v>35.902174</v>
+        <v>35.902174000000002</v>
       </c>
       <c r="T57">
-        <v>2.403344</v>
+        <v>2.4033440000000001</v>
       </c>
       <c r="U57">
         <v>327</v>
       </c>
       <c r="V57">
-        <v>2.84744</v>
+        <v>2.8474400000000002</v>
       </c>
       <c r="W57">
-        <v>30.302752</v>
+        <v>30.302752000000002</v>
       </c>
       <c r="X57">
         <v>225</v>
@@ -4874,7 +4869,7 @@
         <v>44.04</v>
       </c>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -4900,7 +4895,7 @@
         <v>431</v>
       </c>
       <c r="I58">
-        <v>1.062645</v>
+        <v>1.0626450000000001</v>
       </c>
       <c r="J58">
         <v>55.375</v>
@@ -4921,13 +4916,13 @@
         <v>458</v>
       </c>
       <c r="P58">
-        <v>967.248908</v>
+        <v>967.24890800000003</v>
       </c>
       <c r="Q58">
         <v>9</v>
       </c>
       <c r="S58">
-        <v>49.222222</v>
+        <v>49.222222000000002</v>
       </c>
       <c r="T58">
         <v>1.965066</v>
@@ -4939,7 +4934,7 @@
         <v>1.965066</v>
       </c>
       <c r="W58">
-        <v>49.222222</v>
+        <v>49.222222000000002</v>
       </c>
       <c r="X58">
         <v>8</v>
@@ -4948,7 +4943,7 @@
         <v>55.375</v>
       </c>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>25</v>
       </c>
@@ -4974,7 +4969,7 @@
         <v>2081</v>
       </c>
       <c r="I59">
-        <v>1.367131</v>
+        <v>1.3671310000000001</v>
       </c>
       <c r="J59">
         <v>90</v>
@@ -4995,16 +4990,16 @@
         <v>2845</v>
       </c>
       <c r="P59">
-        <v>1170.474517</v>
+        <v>1170.4745170000001</v>
       </c>
       <c r="Q59">
         <v>52</v>
       </c>
       <c r="S59">
-        <v>64.038462</v>
+        <v>64.038461999999996</v>
       </c>
       <c r="T59">
-        <v>1.827768</v>
+        <v>1.8277680000000001</v>
       </c>
       <c r="U59">
         <v>62</v>
@@ -5013,7 +5008,7 @@
         <v>2.179262</v>
       </c>
       <c r="W59">
-        <v>53.709677</v>
+        <v>53.709676999999999</v>
       </c>
       <c r="X59">
         <v>37</v>
@@ -5022,7 +5017,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -5048,10 +5043,10 @@
         <v>5102</v>
       </c>
       <c r="I60">
-        <v>1.485496</v>
+        <v>1.4854959999999999</v>
       </c>
       <c r="J60">
-        <v>79.54216867</v>
+        <v>79.542168669999995</v>
       </c>
       <c r="K60" t="s">
         <v>42</v>
@@ -5069,13 +5064,13 @@
         <v>7579</v>
       </c>
       <c r="P60">
-        <v>871.091173</v>
+        <v>871.09117300000003</v>
       </c>
       <c r="Q60">
         <v>101</v>
       </c>
       <c r="S60">
-        <v>65.366337</v>
+        <v>65.366337000000001</v>
       </c>
       <c r="T60">
         <v>1.33263</v>
@@ -5087,16 +5082,16 @@
         <v>1.477768</v>
       </c>
       <c r="W60">
-        <v>58.946429</v>
+        <v>58.946429000000002</v>
       </c>
       <c r="X60">
         <v>83</v>
       </c>
       <c r="Y60">
-        <v>79.542169</v>
-      </c>
-    </row>
-    <row r="61" spans="1:25">
+        <v>79.542169000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>25</v>
       </c>
@@ -5122,10 +5117,10 @@
         <v>6508</v>
       </c>
       <c r="I61">
-        <v>1.370774</v>
+        <v>1.3707739999999999</v>
       </c>
       <c r="J61">
-        <v>79.3253012</v>
+        <v>79.325301199999998</v>
       </c>
       <c r="K61" t="s">
         <v>42</v>
@@ -5143,16 +5138,16 @@
         <v>8921</v>
       </c>
       <c r="P61">
-        <v>738.033853</v>
+        <v>738.03385300000002</v>
       </c>
       <c r="Q61">
         <v>87</v>
       </c>
       <c r="S61">
-        <v>75.678161</v>
+        <v>75.678161000000003</v>
       </c>
       <c r="T61">
-        <v>0.975227</v>
+        <v>0.97522699999999996</v>
       </c>
       <c r="U61">
         <v>105</v>
@@ -5161,16 +5156,16 @@
         <v>1.176998</v>
       </c>
       <c r="W61">
-        <v>62.704762</v>
+        <v>62.704762000000002</v>
       </c>
       <c r="X61">
         <v>83</v>
       </c>
       <c r="Y61">
-        <v>79.325301</v>
-      </c>
-    </row>
-    <row r="62" spans="1:25">
+        <v>79.325300999999996</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>25</v>
       </c>
@@ -5196,7 +5191,7 @@
         <v>5283</v>
       </c>
       <c r="I62">
-        <v>1.340337</v>
+        <v>1.3403369999999999</v>
       </c>
       <c r="J62">
         <v>81</v>
@@ -5217,13 +5212,13 @@
         <v>7081</v>
       </c>
       <c r="P62">
-        <v>926.564045</v>
+        <v>926.56404499999996</v>
       </c>
       <c r="Q62">
         <v>94</v>
       </c>
       <c r="S62">
-        <v>69.797872</v>
+        <v>69.797871999999998</v>
       </c>
       <c r="T62">
         <v>1.327496</v>
@@ -5232,10 +5227,10 @@
         <v>105</v>
       </c>
       <c r="V62">
-        <v>1.482841</v>
+        <v>1.4828410000000001</v>
       </c>
       <c r="W62">
-        <v>62.485714</v>
+        <v>62.485714000000002</v>
       </c>
       <c r="X62">
         <v>81</v>
@@ -5244,7 +5239,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>25</v>
       </c>
@@ -5270,10 +5265,10 @@
         <v>7434</v>
       </c>
       <c r="I63">
-        <v>1.24361</v>
+        <v>1.2436100000000001</v>
       </c>
       <c r="J63">
-        <v>71.61956522</v>
+        <v>71.619565219999998</v>
       </c>
       <c r="K63" t="s">
         <v>42</v>
@@ -5291,7 +5286,7 @@
         <v>9245</v>
       </c>
       <c r="P63">
-        <v>712.709573</v>
+        <v>712.70957299999998</v>
       </c>
       <c r="Q63">
         <v>110</v>
@@ -5309,16 +5304,16 @@
         <v>1.308816</v>
       </c>
       <c r="W63">
-        <v>54.454545</v>
+        <v>54.454545000000003</v>
       </c>
       <c r="X63">
         <v>92</v>
       </c>
       <c r="Y63">
-        <v>71.619565</v>
-      </c>
-    </row>
-    <row r="64" spans="1:25">
+        <v>71.619564999999994</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>25</v>
       </c>
@@ -5347,7 +5342,7 @@
         <v>1.536252</v>
       </c>
       <c r="J64">
-        <v>34.06923077</v>
+        <v>34.069230769999997</v>
       </c>
       <c r="K64" t="s">
         <v>42</v>
@@ -5365,7 +5360,7 @@
         <v>5509</v>
       </c>
       <c r="P64">
-        <v>803.957161</v>
+        <v>803.95716100000004</v>
       </c>
       <c r="Q64">
         <v>173</v>
@@ -5374,25 +5369,25 @@
         <v>25.601156</v>
       </c>
       <c r="T64">
-        <v>3.140316</v>
+        <v>3.1403159999999999</v>
       </c>
       <c r="U64">
         <v>198</v>
       </c>
       <c r="V64">
-        <v>3.594119</v>
+        <v>3.5941190000000001</v>
       </c>
       <c r="W64">
-        <v>22.368687</v>
+        <v>22.368687000000001</v>
       </c>
       <c r="X64">
         <v>130</v>
       </c>
       <c r="Y64">
-        <v>34.069231</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25">
+        <v>34.069231000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>25</v>
       </c>
@@ -5439,25 +5434,25 @@
         <v>4050</v>
       </c>
       <c r="P65">
-        <v>817.530864</v>
+        <v>817.53086399999995</v>
       </c>
       <c r="Q65">
         <v>265</v>
       </c>
       <c r="S65">
-        <v>12.49434</v>
+        <v>12.494339999999999</v>
       </c>
       <c r="T65">
-        <v>6.54321</v>
+        <v>6.5432100000000002</v>
       </c>
       <c r="U65">
         <v>340</v>
       </c>
       <c r="V65">
-        <v>8.395062</v>
+        <v>8.3950619999999994</v>
       </c>
       <c r="W65">
-        <v>9.738235</v>
+        <v>9.7382349999999995</v>
       </c>
       <c r="X65">
         <v>212</v>
@@ -5466,7 +5461,7 @@
         <v>15.617925</v>
       </c>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>25</v>
       </c>
@@ -5492,10 +5487,10 @@
         <v>2548</v>
       </c>
       <c r="I66">
-        <v>1.425039</v>
+        <v>1.4250389999999999</v>
       </c>
       <c r="J66">
-        <v>62.56603774</v>
+        <v>62.566037739999999</v>
       </c>
       <c r="K66" t="s">
         <v>42</v>
@@ -5513,34 +5508,34 @@
         <v>3631</v>
       </c>
       <c r="P66">
-        <v>913.247039</v>
+        <v>913.24703899999997</v>
       </c>
       <c r="Q66">
         <v>63</v>
       </c>
       <c r="S66">
-        <v>52.634921</v>
+        <v>52.634920999999999</v>
       </c>
       <c r="T66">
-        <v>1.735059</v>
+        <v>1.7350589999999999</v>
       </c>
       <c r="U66">
         <v>74</v>
       </c>
       <c r="V66">
-        <v>2.038006</v>
+        <v>2.0380060000000002</v>
       </c>
       <c r="W66">
-        <v>44.810811</v>
+        <v>44.810811000000001</v>
       </c>
       <c r="X66">
         <v>53</v>
       </c>
       <c r="Y66">
-        <v>62.566038</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25">
+        <v>62.566037999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>25</v>
       </c>
@@ -5569,7 +5564,7 @@
         <v>1.537601</v>
       </c>
       <c r="J67">
-        <v>33.37755102</v>
+        <v>33.377551019999999</v>
       </c>
       <c r="K67" t="s">
         <v>42</v>
@@ -5587,16 +5582,16 @@
         <v>3987</v>
       </c>
       <c r="P67">
-        <v>820.416353</v>
+        <v>820.41635299999996</v>
       </c>
       <c r="Q67">
         <v>110</v>
       </c>
       <c r="S67">
-        <v>29.736364</v>
+        <v>29.736363999999998</v>
       </c>
       <c r="T67">
-        <v>2.758967</v>
+        <v>2.7589670000000002</v>
       </c>
       <c r="U67">
         <v>155</v>
@@ -5605,16 +5600,16 @@
         <v>3.887635</v>
       </c>
       <c r="W67">
-        <v>21.103226</v>
+        <v>21.103225999999999</v>
       </c>
       <c r="X67">
         <v>98</v>
       </c>
       <c r="Y67">
-        <v>33.377551</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25">
+        <v>33.377550999999997</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>25</v>
       </c>
@@ -5661,7 +5656,7 @@
         <v>3043</v>
       </c>
       <c r="P68">
-        <v>934.604009</v>
+        <v>934.60400900000002</v>
       </c>
       <c r="Q68">
         <v>60</v>
@@ -5676,10 +5671,10 @@
         <v>84</v>
       </c>
       <c r="V68">
-        <v>2.760434</v>
+        <v>2.7604340000000001</v>
       </c>
       <c r="W68">
-        <v>33.857143</v>
+        <v>33.857143000000001</v>
       </c>
       <c r="X68">
         <v>50</v>
@@ -5688,7 +5683,7 @@
         <v>56.88</v>
       </c>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>25</v>
       </c>
@@ -5714,10 +5709,10 @@
         <v>2202</v>
       </c>
       <c r="I69">
-        <v>1.201181</v>
+        <v>1.2011810000000001</v>
       </c>
       <c r="J69">
-        <v>53.13207547</v>
+        <v>53.132075469999997</v>
       </c>
       <c r="K69" t="s">
         <v>42</v>
@@ -5735,7 +5730,7 @@
         <v>2645</v>
       </c>
       <c r="P69">
-        <v>1064.650284</v>
+        <v>1064.6502840000001</v>
       </c>
       <c r="Q69">
         <v>58</v>
@@ -5744,13 +5739,13 @@
         <v>48.551724</v>
       </c>
       <c r="T69">
-        <v>2.192817</v>
+        <v>2.1928169999999998</v>
       </c>
       <c r="U69">
         <v>64</v>
       </c>
       <c r="V69">
-        <v>2.41966</v>
+        <v>2.4196599999999999</v>
       </c>
       <c r="W69">
         <v>44</v>
@@ -5762,7 +5757,7 @@
         <v>53.132075</v>
       </c>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>25</v>
       </c>
@@ -5788,7 +5783,7 @@
         <v>770</v>
       </c>
       <c r="I70">
-        <v>1.090909</v>
+        <v>1.0909089999999999</v>
       </c>
       <c r="J70">
         <v>83.92307692</v>
@@ -5815,7 +5810,7 @@
         <v>15</v>
       </c>
       <c r="S70">
-        <v>72.733333</v>
+        <v>72.733333000000002</v>
       </c>
       <c r="T70">
         <v>1.785714</v>
@@ -5824,7 +5819,7 @@
         <v>20</v>
       </c>
       <c r="V70">
-        <v>2.380952</v>
+        <v>2.3809520000000002</v>
       </c>
       <c r="W70">
         <v>54.55</v>
@@ -5833,10 +5828,10 @@
         <v>13</v>
       </c>
       <c r="Y70">
-        <v>83.923077</v>
-      </c>
-    </row>
-    <row r="71" spans="1:25">
+        <v>83.923077000000006</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>25</v>
       </c>
@@ -5862,10 +5857,10 @@
         <v>1076</v>
       </c>
       <c r="I71">
-        <v>1.189591</v>
+        <v>1.1895910000000001</v>
       </c>
       <c r="J71">
-        <v>35.03225806</v>
+        <v>35.032258059999997</v>
       </c>
       <c r="K71" t="s">
         <v>42</v>
@@ -5907,10 +5902,10 @@
         <v>31</v>
       </c>
       <c r="Y71">
-        <v>35.032258</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25">
+        <v>35.032257999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>25</v>
       </c>
@@ -5939,7 +5934,7 @@
         <v>1.194196</v>
       </c>
       <c r="J72">
-        <v>81.23076923</v>
+        <v>81.230769230000007</v>
       </c>
       <c r="K72" t="s">
         <v>42</v>
@@ -5963,10 +5958,10 @@
         <v>13</v>
       </c>
       <c r="S72">
-        <v>81.230769</v>
+        <v>81.230768999999995</v>
       </c>
       <c r="T72">
-        <v>1.214953</v>
+        <v>1.2149529999999999</v>
       </c>
       <c r="U72">
         <v>20</v>
@@ -5981,10 +5976,10 @@
         <v>13</v>
       </c>
       <c r="Y72">
-        <v>81.230769</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25">
+        <v>81.230768999999995</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>25</v>
       </c>
@@ -6010,10 +6005,10 @@
         <v>926</v>
       </c>
       <c r="I73">
-        <v>1.233261</v>
+        <v>1.2332609999999999</v>
       </c>
       <c r="J73">
-        <v>51.9047619</v>
+        <v>51.904761899999997</v>
       </c>
       <c r="K73" t="s">
         <v>42</v>
@@ -6031,22 +6026,22 @@
         <v>1142</v>
       </c>
       <c r="P73">
-        <v>954.465849</v>
+        <v>954.46584900000005</v>
       </c>
       <c r="Q73">
         <v>31</v>
       </c>
       <c r="S73">
-        <v>35.16129</v>
+        <v>35.161290000000001</v>
       </c>
       <c r="T73">
-        <v>2.714536</v>
+        <v>2.7145359999999998</v>
       </c>
       <c r="U73">
         <v>41</v>
       </c>
       <c r="V73">
-        <v>3.590193</v>
+        <v>3.5901930000000002</v>
       </c>
       <c r="W73">
         <v>26.585366</v>
@@ -6055,10 +6050,10 @@
         <v>21</v>
       </c>
       <c r="Y73">
-        <v>51.904762</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25">
+        <v>51.904761999999998</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -6087,7 +6082,7 @@
         <v>1.256116</v>
       </c>
       <c r="J74">
-        <v>64.84848485</v>
+        <v>64.848484850000006</v>
       </c>
       <c r="K74" t="s">
         <v>42</v>
@@ -6105,7 +6100,7 @@
         <v>2516</v>
       </c>
       <c r="P74">
-        <v>850.556439</v>
+        <v>850.55643899999995</v>
       </c>
       <c r="Q74">
         <v>44</v>
@@ -6114,25 +6109,25 @@
         <v>48.636364</v>
       </c>
       <c r="T74">
-        <v>1.748808</v>
+        <v>1.7488079999999999</v>
       </c>
       <c r="U74">
         <v>61</v>
       </c>
       <c r="V74">
-        <v>2.424483</v>
+        <v>2.4244829999999999</v>
       </c>
       <c r="W74">
-        <v>35.081967</v>
+        <v>35.081966999999999</v>
       </c>
       <c r="X74">
         <v>33</v>
       </c>
       <c r="Y74">
-        <v>64.848485</v>
-      </c>
-    </row>
-    <row r="75" spans="1:25">
+        <v>64.848484999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>25</v>
       </c>
@@ -6158,10 +6153,10 @@
         <v>1078</v>
       </c>
       <c r="I75">
-        <v>1.16141</v>
+        <v>1.1614100000000001</v>
       </c>
       <c r="J75">
-        <v>26.675</v>
+        <v>26.675000000000001</v>
       </c>
       <c r="K75" t="s">
         <v>42</v>
@@ -6179,13 +6174,13 @@
         <v>1252</v>
       </c>
       <c r="P75">
-        <v>852.236422</v>
+        <v>852.23642199999995</v>
       </c>
       <c r="Q75">
         <v>45</v>
       </c>
       <c r="S75">
-        <v>23.711111</v>
+        <v>23.711110999999999</v>
       </c>
       <c r="T75">
         <v>3.594249</v>
@@ -6194,7 +6189,7 @@
         <v>54</v>
       </c>
       <c r="V75">
-        <v>4.313099</v>
+        <v>4.3130990000000002</v>
       </c>
       <c r="W75">
         <v>19.759259</v>
@@ -6203,10 +6198,10 @@
         <v>40</v>
       </c>
       <c r="Y75">
-        <v>26.675</v>
-      </c>
-    </row>
-    <row r="76" spans="1:25">
+        <v>26.675000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -6253,25 +6248,25 @@
         <v>1222</v>
       </c>
       <c r="P76">
-        <v>887.070376</v>
+        <v>887.07037600000001</v>
       </c>
       <c r="Q76">
         <v>38</v>
       </c>
       <c r="S76">
-        <v>28.526316</v>
+        <v>28.526316000000001</v>
       </c>
       <c r="T76">
-        <v>3.109656</v>
+        <v>3.1096560000000002</v>
       </c>
       <c r="U76">
         <v>43</v>
       </c>
       <c r="V76">
-        <v>3.518822</v>
+        <v>3.5188220000000001</v>
       </c>
       <c r="W76">
-        <v>25.209302</v>
+        <v>25.209302000000001</v>
       </c>
       <c r="X76">
         <v>32</v>
@@ -6280,7 +6275,7 @@
         <v>33.875</v>
       </c>
     </row>
-    <row r="77" spans="1:25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>25</v>
       </c>
@@ -6331,17 +6326,8 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <printOptions gridLines="false" gridLinesSet="true"/>
+  <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
--- a/data/monthly/【2026年5月】月次数値.xlsx
+++ b/data/monthly/【2026年5月】月次数値.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="188">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -439,6 +439,150 @@
   </si>
   <si>
     <t>2026-07-14</t>
+  </si>
+  <si>
+    <t>鍼灸サロンNOA</t>
+  </si>
+  <si>
+    <t>有限会社 ムネケン</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>堀田歯科</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2027-05-01</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック（2年目）</t>
+  </si>
+  <si>
+    <t>2026-04-02</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科（2回目）</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>掛川整体院サウレ</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>スカイハイ英語塾</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>アキュラデンタルクリニック</t>
+  </si>
+  <si>
+    <t>UESUGI美容鍼灸整骨院</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>PML　広尾店</t>
+  </si>
+  <si>
+    <t>Healing Salon Ange</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>DesignBody 御徒町店</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>Beauty Salon Arona</t>
   </si>
 </sst>
 </file>
@@ -789,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y77"/>
+  <dimension ref="A1:Y109"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -6323,6 +6467,2242 @@
       </c>
       <c r="W77">
         <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
+        <v>187</v>
+      </c>
+      <c r="D78" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78" t="s">
+        <v>29</v>
+      </c>
+      <c r="F78">
+        <v>37</v>
+      </c>
+      <c r="G78" t="s">
+        <v>41</v>
+      </c>
+      <c r="H78">
+        <v>3145</v>
+      </c>
+      <c r="I78">
+        <v>1.7027030000000001</v>
+      </c>
+      <c r="J78">
+        <v>144.62162162000001</v>
+      </c>
+      <c r="K78" t="s">
+        <v>42</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>5351</v>
+      </c>
+      <c r="N78" t="s">
+        <v>57</v>
+      </c>
+      <c r="O78">
+        <v>5355</v>
+      </c>
+      <c r="P78">
+        <v>999.25303499999995</v>
+      </c>
+      <c r="Q78">
+        <v>71</v>
+      </c>
+      <c r="S78">
+        <v>75.366197</v>
+      </c>
+      <c r="T78">
+        <v>1.3258639999999999</v>
+      </c>
+      <c r="U78">
+        <v>85</v>
+      </c>
+      <c r="V78">
+        <v>1.587302</v>
+      </c>
+      <c r="W78">
+        <v>62.952941000000003</v>
+      </c>
+      <c r="X78">
+        <v>37</v>
+      </c>
+      <c r="Y78">
+        <v>144.621622</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" t="s">
+        <v>186</v>
+      </c>
+      <c r="D79" t="s">
+        <v>144</v>
+      </c>
+      <c r="E79" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79">
+        <v>111</v>
+      </c>
+      <c r="G79" t="s">
+        <v>30</v>
+      </c>
+      <c r="H79">
+        <v>1787</v>
+      </c>
+      <c r="I79">
+        <v>1.1628430000000001</v>
+      </c>
+      <c r="J79">
+        <v>31.648648649999998</v>
+      </c>
+      <c r="K79" t="s">
+        <v>42</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>3513</v>
+      </c>
+      <c r="N79" t="s">
+        <v>185</v>
+      </c>
+      <c r="O79">
+        <v>2078</v>
+      </c>
+      <c r="P79">
+        <v>1690.5678539999999</v>
+      </c>
+      <c r="Q79">
+        <v>111</v>
+      </c>
+      <c r="S79">
+        <v>31.648648999999999</v>
+      </c>
+      <c r="T79">
+        <v>5.3416750000000004</v>
+      </c>
+      <c r="U79">
+        <v>116</v>
+      </c>
+      <c r="V79">
+        <v>5.5822909999999997</v>
+      </c>
+      <c r="W79">
+        <v>30.284483000000002</v>
+      </c>
+      <c r="X79">
+        <v>3</v>
+      </c>
+      <c r="Y79">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" t="s">
+        <v>184</v>
+      </c>
+      <c r="D80" t="s">
+        <v>144</v>
+      </c>
+      <c r="E80" t="s">
+        <v>29</v>
+      </c>
+      <c r="F80">
+        <v>57</v>
+      </c>
+      <c r="G80" t="s">
+        <v>41</v>
+      </c>
+      <c r="H80">
+        <v>2441</v>
+      </c>
+      <c r="I80">
+        <v>1.386317</v>
+      </c>
+      <c r="J80">
+        <v>72.228070180000003</v>
+      </c>
+      <c r="K80" t="s">
+        <v>42</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>4117</v>
+      </c>
+      <c r="N80" t="s">
+        <v>180</v>
+      </c>
+      <c r="O80">
+        <v>3384</v>
+      </c>
+      <c r="P80">
+        <v>1216.607565</v>
+      </c>
+      <c r="Q80">
+        <v>73</v>
+      </c>
+      <c r="S80">
+        <v>56.397260000000003</v>
+      </c>
+      <c r="T80">
+        <v>2.1572100000000001</v>
+      </c>
+      <c r="U80">
+        <v>76</v>
+      </c>
+      <c r="V80">
+        <v>2.2458629999999999</v>
+      </c>
+      <c r="W80">
+        <v>54.171053000000001</v>
+      </c>
+      <c r="X80">
+        <v>57</v>
+      </c>
+      <c r="Y80">
+        <v>72.228070000000002</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>183</v>
+      </c>
+      <c r="D81" t="s">
+        <v>144</v>
+      </c>
+      <c r="E81" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81">
+        <v>82</v>
+      </c>
+      <c r="G81" t="s">
+        <v>30</v>
+      </c>
+      <c r="H81">
+        <v>3783</v>
+      </c>
+      <c r="I81">
+        <v>1.5440130000000001</v>
+      </c>
+      <c r="J81">
+        <v>46.353658539999998</v>
+      </c>
+      <c r="K81" t="s">
+        <v>42</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>3801</v>
+      </c>
+      <c r="N81" t="s">
+        <v>170</v>
+      </c>
+      <c r="O81">
+        <v>5841</v>
+      </c>
+      <c r="P81">
+        <v>650.74473499999999</v>
+      </c>
+      <c r="Q81">
+        <v>82</v>
+      </c>
+      <c r="S81">
+        <v>46.353659</v>
+      </c>
+      <c r="T81">
+        <v>1.403869</v>
+      </c>
+      <c r="U81">
+        <v>86</v>
+      </c>
+      <c r="V81">
+        <v>1.472351</v>
+      </c>
+      <c r="W81">
+        <v>44.197673999999999</v>
+      </c>
+      <c r="X81">
+        <v>69</v>
+      </c>
+      <c r="Y81">
+        <v>55.086956999999998</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>182</v>
+      </c>
+      <c r="D82" t="s">
+        <v>28</v>
+      </c>
+      <c r="E82" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82">
+        <v>42</v>
+      </c>
+      <c r="G82" t="s">
+        <v>41</v>
+      </c>
+      <c r="H82">
+        <v>2267</v>
+      </c>
+      <c r="I82">
+        <v>1.473754</v>
+      </c>
+      <c r="J82">
+        <v>136.07142856999999</v>
+      </c>
+      <c r="K82" t="s">
+        <v>42</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>5715</v>
+      </c>
+      <c r="N82" t="s">
+        <v>65</v>
+      </c>
+      <c r="O82">
+        <v>3341</v>
+      </c>
+      <c r="P82">
+        <v>1710.565699</v>
+      </c>
+      <c r="Q82">
+        <v>92</v>
+      </c>
+      <c r="S82">
+        <v>62.119565000000001</v>
+      </c>
+      <c r="T82">
+        <v>2.7536670000000001</v>
+      </c>
+      <c r="U82">
+        <v>107</v>
+      </c>
+      <c r="V82">
+        <v>3.2026340000000002</v>
+      </c>
+      <c r="W82">
+        <v>53.411214999999999</v>
+      </c>
+      <c r="X82">
+        <v>42</v>
+      </c>
+      <c r="Y82">
+        <v>136.07142899999999</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="s">
+        <v>181</v>
+      </c>
+      <c r="D83" t="s">
+        <v>45</v>
+      </c>
+      <c r="E83" t="s">
+        <v>29</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="K83" t="s">
+        <v>42</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83" t="s">
+        <v>180</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
+        <v>179</v>
+      </c>
+      <c r="D84" t="s">
+        <v>28</v>
+      </c>
+      <c r="E84" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84">
+        <v>99</v>
+      </c>
+      <c r="G84" t="s">
+        <v>41</v>
+      </c>
+      <c r="H84">
+        <v>2954</v>
+      </c>
+      <c r="I84">
+        <v>1.429926</v>
+      </c>
+      <c r="J84">
+        <v>53.878787879999997</v>
+      </c>
+      <c r="K84" t="s">
+        <v>42</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>5334</v>
+      </c>
+      <c r="N84" t="s">
+        <v>63</v>
+      </c>
+      <c r="O84">
+        <v>4224</v>
+      </c>
+      <c r="P84">
+        <v>1262.784091</v>
+      </c>
+      <c r="Q84">
+        <v>115</v>
+      </c>
+      <c r="S84">
+        <v>46.382609000000002</v>
+      </c>
+      <c r="T84">
+        <v>2.7225380000000001</v>
+      </c>
+      <c r="U84">
+        <v>126</v>
+      </c>
+      <c r="V84">
+        <v>2.982955</v>
+      </c>
+      <c r="W84">
+        <v>42.333333000000003</v>
+      </c>
+      <c r="X84">
+        <v>99</v>
+      </c>
+      <c r="Y84">
+        <v>53.878788</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s">
+        <v>178</v>
+      </c>
+      <c r="D85" t="s">
+        <v>28</v>
+      </c>
+      <c r="E85" t="s">
+        <v>29</v>
+      </c>
+      <c r="F85">
+        <v>488</v>
+      </c>
+      <c r="G85" t="s">
+        <v>41</v>
+      </c>
+      <c r="H85">
+        <v>10000</v>
+      </c>
+      <c r="I85">
+        <v>1.504</v>
+      </c>
+      <c r="J85">
+        <v>44.084016390000002</v>
+      </c>
+      <c r="K85" t="s">
+        <v>42</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>21513</v>
+      </c>
+      <c r="N85" t="s">
+        <v>177</v>
+      </c>
+      <c r="O85">
+        <v>15040</v>
+      </c>
+      <c r="P85">
+        <v>1430.385638</v>
+      </c>
+      <c r="Q85">
+        <v>672</v>
+      </c>
+      <c r="S85">
+        <v>32.013393000000001</v>
+      </c>
+      <c r="T85">
+        <v>4.4680850000000003</v>
+      </c>
+      <c r="U85">
+        <v>740</v>
+      </c>
+      <c r="V85">
+        <v>4.9202130000000004</v>
+      </c>
+      <c r="W85">
+        <v>29.071622000000001</v>
+      </c>
+      <c r="X85">
+        <v>488</v>
+      </c>
+      <c r="Y85">
+        <v>44.084015999999998</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>176</v>
+      </c>
+      <c r="D86" t="s">
+        <v>45</v>
+      </c>
+      <c r="E86" t="s">
+        <v>29</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="K86" t="s">
+        <v>42</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86" t="s">
+        <v>142</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" t="s">
+        <v>175</v>
+      </c>
+      <c r="D87" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87">
+        <v>108</v>
+      </c>
+      <c r="G87" t="s">
+        <v>41</v>
+      </c>
+      <c r="H87">
+        <v>3927</v>
+      </c>
+      <c r="I87">
+        <v>1.427044</v>
+      </c>
+      <c r="J87">
+        <v>46.583333330000002</v>
+      </c>
+      <c r="K87" t="s">
+        <v>42</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>5031</v>
+      </c>
+      <c r="N87" t="s">
+        <v>174</v>
+      </c>
+      <c r="O87">
+        <v>5604</v>
+      </c>
+      <c r="P87">
+        <v>897.75160600000004</v>
+      </c>
+      <c r="Q87">
+        <v>187</v>
+      </c>
+      <c r="S87">
+        <v>26.903742999999999</v>
+      </c>
+      <c r="T87">
+        <v>3.3369019999999998</v>
+      </c>
+      <c r="U87">
+        <v>195</v>
+      </c>
+      <c r="V87">
+        <v>3.479657</v>
+      </c>
+      <c r="W87">
+        <v>25.8</v>
+      </c>
+      <c r="X87">
+        <v>108</v>
+      </c>
+      <c r="Y87">
+        <v>46.583333000000003</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" t="s">
+        <v>173</v>
+      </c>
+      <c r="D88" t="s">
+        <v>28</v>
+      </c>
+      <c r="E88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88">
+        <v>106</v>
+      </c>
+      <c r="G88" t="s">
+        <v>30</v>
+      </c>
+      <c r="H88">
+        <v>3560</v>
+      </c>
+      <c r="I88">
+        <v>1.670787</v>
+      </c>
+      <c r="J88">
+        <v>45.556603770000002</v>
+      </c>
+      <c r="K88" t="s">
+        <v>42</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>4829</v>
+      </c>
+      <c r="N88" t="s">
+        <v>172</v>
+      </c>
+      <c r="O88">
+        <v>5948</v>
+      </c>
+      <c r="P88">
+        <v>811.86953600000004</v>
+      </c>
+      <c r="Q88">
+        <v>106</v>
+      </c>
+      <c r="S88">
+        <v>45.556604</v>
+      </c>
+      <c r="T88">
+        <v>1.7821119999999999</v>
+      </c>
+      <c r="U88">
+        <v>117</v>
+      </c>
+      <c r="V88">
+        <v>1.9670479999999999</v>
+      </c>
+      <c r="W88">
+        <v>41.273504000000003</v>
+      </c>
+      <c r="X88">
+        <v>80</v>
+      </c>
+      <c r="Y88">
+        <v>60.362499999999997</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
+        <v>171</v>
+      </c>
+      <c r="D89" t="s">
+        <v>144</v>
+      </c>
+      <c r="E89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F89">
+        <v>102</v>
+      </c>
+      <c r="G89" t="s">
+        <v>30</v>
+      </c>
+      <c r="H89">
+        <v>2304</v>
+      </c>
+      <c r="I89">
+        <v>1.1462669999999999</v>
+      </c>
+      <c r="J89">
+        <v>37.10784314</v>
+      </c>
+      <c r="K89" t="s">
+        <v>42</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>3785</v>
+      </c>
+      <c r="N89" t="s">
+        <v>170</v>
+      </c>
+      <c r="O89">
+        <v>2641</v>
+      </c>
+      <c r="P89">
+        <v>1433.1692539999999</v>
+      </c>
+      <c r="Q89">
+        <v>102</v>
+      </c>
+      <c r="S89">
+        <v>37.107843000000003</v>
+      </c>
+      <c r="T89">
+        <v>3.8621729999999999</v>
+      </c>
+      <c r="U89">
+        <v>110</v>
+      </c>
+      <c r="V89">
+        <v>4.165089</v>
+      </c>
+      <c r="W89">
+        <v>34.409090999999997</v>
+      </c>
+      <c r="X89">
+        <v>70</v>
+      </c>
+      <c r="Y89">
+        <v>54.071429000000002</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s">
+        <v>169</v>
+      </c>
+      <c r="D90" t="s">
+        <v>144</v>
+      </c>
+      <c r="E90" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90">
+        <v>131</v>
+      </c>
+      <c r="G90" t="s">
+        <v>30</v>
+      </c>
+      <c r="H90">
+        <v>2011</v>
+      </c>
+      <c r="I90">
+        <v>1.2550969999999999</v>
+      </c>
+      <c r="J90">
+        <v>27.38931298</v>
+      </c>
+      <c r="K90" t="s">
+        <v>42</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>3588</v>
+      </c>
+      <c r="N90" t="s">
+        <v>157</v>
+      </c>
+      <c r="O90">
+        <v>2524</v>
+      </c>
+      <c r="P90">
+        <v>1421.5530900000001</v>
+      </c>
+      <c r="Q90">
+        <v>131</v>
+      </c>
+      <c r="S90">
+        <v>27.389313000000001</v>
+      </c>
+      <c r="T90">
+        <v>5.1901739999999998</v>
+      </c>
+      <c r="U90">
+        <v>135</v>
+      </c>
+      <c r="V90">
+        <v>5.3486529999999997</v>
+      </c>
+      <c r="W90">
+        <v>26.577777999999999</v>
+      </c>
+      <c r="X90">
+        <v>2</v>
+      </c>
+      <c r="Y90">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" t="s">
+        <v>168</v>
+      </c>
+      <c r="D91" t="s">
+        <v>28</v>
+      </c>
+      <c r="E91" t="s">
+        <v>29</v>
+      </c>
+      <c r="F91">
+        <v>83</v>
+      </c>
+      <c r="G91" t="s">
+        <v>30</v>
+      </c>
+      <c r="H91">
+        <v>3072</v>
+      </c>
+      <c r="I91">
+        <v>1.489258</v>
+      </c>
+      <c r="J91">
+        <v>54.710843369999999</v>
+      </c>
+      <c r="K91" t="s">
+        <v>42</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>4541</v>
+      </c>
+      <c r="N91" t="s">
+        <v>167</v>
+      </c>
+      <c r="O91">
+        <v>4575</v>
+      </c>
+      <c r="P91">
+        <v>992.56830600000001</v>
+      </c>
+      <c r="Q91">
+        <v>83</v>
+      </c>
+      <c r="S91">
+        <v>54.710842999999997</v>
+      </c>
+      <c r="T91">
+        <v>1.814208</v>
+      </c>
+      <c r="U91">
+        <v>83</v>
+      </c>
+      <c r="V91">
+        <v>1.814208</v>
+      </c>
+      <c r="W91">
+        <v>54.710842999999997</v>
+      </c>
+      <c r="X91">
+        <v>47</v>
+      </c>
+      <c r="Y91">
+        <v>96.617020999999994</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>25</v>
+      </c>
+      <c r="B92" t="s">
+        <v>26</v>
+      </c>
+      <c r="C92" t="s">
+        <v>166</v>
+      </c>
+      <c r="D92" t="s">
+        <v>144</v>
+      </c>
+      <c r="E92" t="s">
+        <v>29</v>
+      </c>
+      <c r="F92">
+        <v>151</v>
+      </c>
+      <c r="G92" t="s">
+        <v>30</v>
+      </c>
+      <c r="H92">
+        <v>2656</v>
+      </c>
+      <c r="I92">
+        <v>1.1073040000000001</v>
+      </c>
+      <c r="J92">
+        <v>24.98675497</v>
+      </c>
+      <c r="K92" t="s">
+        <v>42</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>3773</v>
+      </c>
+      <c r="N92" t="s">
+        <v>146</v>
+      </c>
+      <c r="O92">
+        <v>2941</v>
+      </c>
+      <c r="P92">
+        <v>1282.896974</v>
+      </c>
+      <c r="Q92">
+        <v>151</v>
+      </c>
+      <c r="S92">
+        <v>24.986754999999999</v>
+      </c>
+      <c r="T92">
+        <v>5.1343079999999999</v>
+      </c>
+      <c r="U92">
+        <v>164</v>
+      </c>
+      <c r="V92">
+        <v>5.5763350000000003</v>
+      </c>
+      <c r="W92">
+        <v>23.006098000000001</v>
+      </c>
+      <c r="X92">
+        <v>5</v>
+      </c>
+      <c r="Y92">
+        <v>754.6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>25</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" t="s">
+        <v>165</v>
+      </c>
+      <c r="D93" t="s">
+        <v>28</v>
+      </c>
+      <c r="E93" t="s">
+        <v>29</v>
+      </c>
+      <c r="F93">
+        <v>250</v>
+      </c>
+      <c r="G93" t="s">
+        <v>30</v>
+      </c>
+      <c r="H93">
+        <v>3776</v>
+      </c>
+      <c r="I93">
+        <v>1.283633</v>
+      </c>
+      <c r="J93">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="K93" t="s">
+        <v>42</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>4640</v>
+      </c>
+      <c r="N93" t="s">
+        <v>164</v>
+      </c>
+      <c r="O93">
+        <v>4847</v>
+      </c>
+      <c r="P93">
+        <v>957.29317100000003</v>
+      </c>
+      <c r="Q93">
+        <v>250</v>
+      </c>
+      <c r="S93">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="T93">
+        <v>5.1578299999999997</v>
+      </c>
+      <c r="U93">
+        <v>256</v>
+      </c>
+      <c r="V93">
+        <v>5.2816179999999999</v>
+      </c>
+      <c r="W93">
+        <v>18.125</v>
+      </c>
+      <c r="X93">
+        <v>195</v>
+      </c>
+      <c r="Y93">
+        <v>23.794872000000002</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>25</v>
+      </c>
+      <c r="B94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C94" t="s">
+        <v>163</v>
+      </c>
+      <c r="D94" t="s">
+        <v>28</v>
+      </c>
+      <c r="E94" t="s">
+        <v>29</v>
+      </c>
+      <c r="F94">
+        <v>204</v>
+      </c>
+      <c r="G94" t="s">
+        <v>41</v>
+      </c>
+      <c r="H94">
+        <v>4588</v>
+      </c>
+      <c r="I94">
+        <v>1.5357449999999999</v>
+      </c>
+      <c r="J94">
+        <v>28.887254899999999</v>
+      </c>
+      <c r="K94" t="s">
+        <v>42</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>5893</v>
+      </c>
+      <c r="N94" t="s">
+        <v>73</v>
+      </c>
+      <c r="O94">
+        <v>7046</v>
+      </c>
+      <c r="P94">
+        <v>836.36105599999996</v>
+      </c>
+      <c r="Q94">
+        <v>224</v>
+      </c>
+      <c r="S94">
+        <v>26.308036000000001</v>
+      </c>
+      <c r="T94">
+        <v>3.179109</v>
+      </c>
+      <c r="U94">
+        <v>270</v>
+      </c>
+      <c r="V94">
+        <v>3.8319610000000002</v>
+      </c>
+      <c r="W94">
+        <v>21.825925999999999</v>
+      </c>
+      <c r="X94">
+        <v>204</v>
+      </c>
+      <c r="Y94">
+        <v>28.887255</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>25</v>
+      </c>
+      <c r="B95" t="s">
+        <v>26</v>
+      </c>
+      <c r="C95" t="s">
+        <v>162</v>
+      </c>
+      <c r="D95" t="s">
+        <v>144</v>
+      </c>
+      <c r="E95" t="s">
+        <v>29</v>
+      </c>
+      <c r="F95">
+        <v>98</v>
+      </c>
+      <c r="G95" t="s">
+        <v>30</v>
+      </c>
+      <c r="H95">
+        <v>2427</v>
+      </c>
+      <c r="I95">
+        <v>1.299547</v>
+      </c>
+      <c r="J95">
+        <v>37.704081629999997</v>
+      </c>
+      <c r="K95" t="s">
+        <v>42</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>3695</v>
+      </c>
+      <c r="N95" t="s">
+        <v>157</v>
+      </c>
+      <c r="O95">
+        <v>3154</v>
+      </c>
+      <c r="P95">
+        <v>1171.5282179999999</v>
+      </c>
+      <c r="Q95">
+        <v>98</v>
+      </c>
+      <c r="S95">
+        <v>37.704082</v>
+      </c>
+      <c r="T95">
+        <v>3.1071659999999999</v>
+      </c>
+      <c r="U95">
+        <v>109</v>
+      </c>
+      <c r="V95">
+        <v>3.4559289999999998</v>
+      </c>
+      <c r="W95">
+        <v>33.899082999999997</v>
+      </c>
+      <c r="X95">
+        <v>2</v>
+      </c>
+      <c r="Y95">
+        <v>1847.5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>25</v>
+      </c>
+      <c r="B96" t="s">
+        <v>26</v>
+      </c>
+      <c r="C96" t="s">
+        <v>87</v>
+      </c>
+      <c r="D96" t="s">
+        <v>45</v>
+      </c>
+      <c r="E96" t="s">
+        <v>29</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="K96" t="s">
+        <v>42</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96" t="s">
+        <v>161</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+      <c r="U96">
+        <v>0</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>25</v>
+      </c>
+      <c r="B97" t="s">
+        <v>26</v>
+      </c>
+      <c r="C97" t="s">
+        <v>160</v>
+      </c>
+      <c r="D97" t="s">
+        <v>45</v>
+      </c>
+      <c r="E97" t="s">
+        <v>29</v>
+      </c>
+      <c r="F97">
+        <v>106</v>
+      </c>
+      <c r="G97" t="s">
+        <v>41</v>
+      </c>
+      <c r="H97">
+        <v>4135</v>
+      </c>
+      <c r="I97">
+        <v>1.3424430000000001</v>
+      </c>
+      <c r="J97">
+        <v>57.292452830000002</v>
+      </c>
+      <c r="K97" t="s">
+        <v>42</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+      <c r="M97">
+        <v>6073</v>
+      </c>
+      <c r="N97" t="s">
+        <v>77</v>
+      </c>
+      <c r="O97">
+        <v>5551</v>
+      </c>
+      <c r="P97">
+        <v>1094.03711</v>
+      </c>
+      <c r="Q97">
+        <v>136</v>
+      </c>
+      <c r="S97">
+        <v>44.654412000000001</v>
+      </c>
+      <c r="T97">
+        <v>2.4500090000000001</v>
+      </c>
+      <c r="U97">
+        <v>167</v>
+      </c>
+      <c r="V97">
+        <v>3.008467</v>
+      </c>
+      <c r="W97">
+        <v>36.365268999999998</v>
+      </c>
+      <c r="X97">
+        <v>106</v>
+      </c>
+      <c r="Y97">
+        <v>57.292453000000002</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>25</v>
+      </c>
+      <c r="B98" t="s">
+        <v>26</v>
+      </c>
+      <c r="C98" t="s">
+        <v>159</v>
+      </c>
+      <c r="D98" t="s">
+        <v>144</v>
+      </c>
+      <c r="E98" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98">
+        <v>45</v>
+      </c>
+      <c r="G98" t="s">
+        <v>30</v>
+      </c>
+      <c r="H98">
+        <v>1390</v>
+      </c>
+      <c r="I98">
+        <v>2.182734</v>
+      </c>
+      <c r="J98">
+        <v>93</v>
+      </c>
+      <c r="K98" t="s">
+        <v>42</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>4185</v>
+      </c>
+      <c r="N98" t="s">
+        <v>109</v>
+      </c>
+      <c r="O98">
+        <v>3034</v>
+      </c>
+      <c r="P98">
+        <v>1379.367172</v>
+      </c>
+      <c r="Q98">
+        <v>45</v>
+      </c>
+      <c r="S98">
+        <v>93</v>
+      </c>
+      <c r="T98">
+        <v>1.4831909999999999</v>
+      </c>
+      <c r="U98">
+        <v>47</v>
+      </c>
+      <c r="V98">
+        <v>1.54911</v>
+      </c>
+      <c r="W98">
+        <v>89.042552999999998</v>
+      </c>
+      <c r="X98">
+        <v>1</v>
+      </c>
+      <c r="Y98">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>25</v>
+      </c>
+      <c r="B99" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" t="s">
+        <v>158</v>
+      </c>
+      <c r="D99" t="s">
+        <v>144</v>
+      </c>
+      <c r="E99" t="s">
+        <v>29</v>
+      </c>
+      <c r="F99">
+        <v>81</v>
+      </c>
+      <c r="G99" t="s">
+        <v>30</v>
+      </c>
+      <c r="H99">
+        <v>2843</v>
+      </c>
+      <c r="I99">
+        <v>1.3517410000000001</v>
+      </c>
+      <c r="J99">
+        <v>44.790123459999997</v>
+      </c>
+      <c r="K99" t="s">
+        <v>42</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>3628</v>
+      </c>
+      <c r="N99" t="s">
+        <v>157</v>
+      </c>
+      <c r="O99">
+        <v>3843</v>
+      </c>
+      <c r="P99">
+        <v>944.054124</v>
+      </c>
+      <c r="Q99">
+        <v>81</v>
+      </c>
+      <c r="S99">
+        <v>44.790123000000001</v>
+      </c>
+      <c r="T99">
+        <v>2.1077279999999998</v>
+      </c>
+      <c r="U99">
+        <v>91</v>
+      </c>
+      <c r="V99">
+        <v>2.3679420000000002</v>
+      </c>
+      <c r="W99">
+        <v>39.868132000000003</v>
+      </c>
+      <c r="X99">
+        <v>2</v>
+      </c>
+      <c r="Y99">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>25</v>
+      </c>
+      <c r="B100" t="s">
+        <v>26</v>
+      </c>
+      <c r="C100" t="s">
+        <v>156</v>
+      </c>
+      <c r="D100" t="s">
+        <v>28</v>
+      </c>
+      <c r="E100" t="s">
+        <v>29</v>
+      </c>
+      <c r="F100">
+        <v>97</v>
+      </c>
+      <c r="G100" t="s">
+        <v>30</v>
+      </c>
+      <c r="H100">
+        <v>1756</v>
+      </c>
+      <c r="I100">
+        <v>1.199317</v>
+      </c>
+      <c r="J100">
+        <v>44.556701029999999</v>
+      </c>
+      <c r="K100" t="s">
+        <v>42</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>4322</v>
+      </c>
+      <c r="N100" t="s">
+        <v>155</v>
+      </c>
+      <c r="O100">
+        <v>2106</v>
+      </c>
+      <c r="P100">
+        <v>2052.2317189999999</v>
+      </c>
+      <c r="Q100">
+        <v>97</v>
+      </c>
+      <c r="S100">
+        <v>44.556700999999997</v>
+      </c>
+      <c r="T100">
+        <v>4.6058880000000002</v>
+      </c>
+      <c r="U100">
+        <v>98</v>
+      </c>
+      <c r="V100">
+        <v>4.6533709999999999</v>
+      </c>
+      <c r="W100">
+        <v>44.102041</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>25</v>
+      </c>
+      <c r="B101" t="s">
+        <v>26</v>
+      </c>
+      <c r="C101" t="s">
+        <v>154</v>
+      </c>
+      <c r="D101" t="s">
+        <v>144</v>
+      </c>
+      <c r="E101" t="s">
+        <v>29</v>
+      </c>
+      <c r="F101">
+        <v>84</v>
+      </c>
+      <c r="G101" t="s">
+        <v>30</v>
+      </c>
+      <c r="H101">
+        <v>3319</v>
+      </c>
+      <c r="I101">
+        <v>1.373607</v>
+      </c>
+      <c r="J101">
+        <v>45.892857139999997</v>
+      </c>
+      <c r="K101" t="s">
+        <v>42</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>3855</v>
+      </c>
+      <c r="N101" t="s">
+        <v>153</v>
+      </c>
+      <c r="O101">
+        <v>4559</v>
+      </c>
+      <c r="P101">
+        <v>845.58017099999995</v>
+      </c>
+      <c r="Q101">
+        <v>84</v>
+      </c>
+      <c r="S101">
+        <v>45.892856999999999</v>
+      </c>
+      <c r="T101">
+        <v>1.842509</v>
+      </c>
+      <c r="U101">
+        <v>92</v>
+      </c>
+      <c r="V101">
+        <v>2.0179860000000001</v>
+      </c>
+      <c r="W101">
+        <v>41.902174000000002</v>
+      </c>
+      <c r="X101">
+        <v>54</v>
+      </c>
+      <c r="Y101">
+        <v>71.388889000000006</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>25</v>
+      </c>
+      <c r="B102" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" t="s">
+        <v>152</v>
+      </c>
+      <c r="D102" t="s">
+        <v>45</v>
+      </c>
+      <c r="E102" t="s">
+        <v>29</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="K102" t="s">
+        <v>42</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102" t="s">
+        <v>151</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="U102">
+        <v>0</v>
+      </c>
+      <c r="V102">
+        <v>0</v>
+      </c>
+      <c r="W102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>25</v>
+      </c>
+      <c r="B103" t="s">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s">
+        <v>150</v>
+      </c>
+      <c r="D103" t="s">
+        <v>28</v>
+      </c>
+      <c r="E103" t="s">
+        <v>29</v>
+      </c>
+      <c r="F103">
+        <v>53</v>
+      </c>
+      <c r="G103" t="s">
+        <v>41</v>
+      </c>
+      <c r="H103">
+        <v>3663</v>
+      </c>
+      <c r="I103">
+        <v>1.349167</v>
+      </c>
+      <c r="J103">
+        <v>89.037735850000004</v>
+      </c>
+      <c r="K103" t="s">
+        <v>42</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>4719</v>
+      </c>
+      <c r="N103" t="s">
+        <v>149</v>
+      </c>
+      <c r="O103">
+        <v>4942</v>
+      </c>
+      <c r="P103">
+        <v>954.87656800000002</v>
+      </c>
+      <c r="Q103">
+        <v>59</v>
+      </c>
+      <c r="S103">
+        <v>79.983051000000003</v>
+      </c>
+      <c r="T103">
+        <v>1.1938489999999999</v>
+      </c>
+      <c r="U103">
+        <v>78</v>
+      </c>
+      <c r="V103">
+        <v>1.578308</v>
+      </c>
+      <c r="W103">
+        <v>60.5</v>
+      </c>
+      <c r="X103">
+        <v>53</v>
+      </c>
+      <c r="Y103">
+        <v>89.037735999999995</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>25</v>
+      </c>
+      <c r="B104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C104" t="s">
+        <v>107</v>
+      </c>
+      <c r="D104" t="s">
+        <v>144</v>
+      </c>
+      <c r="E104" t="s">
+        <v>29</v>
+      </c>
+      <c r="F104">
+        <v>43</v>
+      </c>
+      <c r="G104" t="s">
+        <v>30</v>
+      </c>
+      <c r="H104">
+        <v>1777</v>
+      </c>
+      <c r="I104">
+        <v>1.250985</v>
+      </c>
+      <c r="J104">
+        <v>69.930232559999993</v>
+      </c>
+      <c r="K104" t="s">
+        <v>42</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>3007</v>
+      </c>
+      <c r="N104" t="s">
+        <v>148</v>
+      </c>
+      <c r="O104">
+        <v>2223</v>
+      </c>
+      <c r="P104">
+        <v>1352.676563</v>
+      </c>
+      <c r="Q104">
+        <v>43</v>
+      </c>
+      <c r="S104">
+        <v>69.930233000000001</v>
+      </c>
+      <c r="T104">
+        <v>1.934323</v>
+      </c>
+      <c r="U104">
+        <v>46</v>
+      </c>
+      <c r="V104">
+        <v>2.0692759999999999</v>
+      </c>
+      <c r="W104">
+        <v>65.369564999999994</v>
+      </c>
+      <c r="X104">
+        <v>1</v>
+      </c>
+      <c r="Y104">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>25</v>
+      </c>
+      <c r="B105" t="s">
+        <v>26</v>
+      </c>
+      <c r="C105" t="s">
+        <v>147</v>
+      </c>
+      <c r="D105" t="s">
+        <v>144</v>
+      </c>
+      <c r="E105" t="s">
+        <v>29</v>
+      </c>
+      <c r="F105">
+        <v>45</v>
+      </c>
+      <c r="G105" t="s">
+        <v>30</v>
+      </c>
+      <c r="H105">
+        <v>1917</v>
+      </c>
+      <c r="I105">
+        <v>1.174752</v>
+      </c>
+      <c r="J105">
+        <v>70.777777779999994</v>
+      </c>
+      <c r="K105" t="s">
+        <v>42</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>3185</v>
+      </c>
+      <c r="N105" t="s">
+        <v>146</v>
+      </c>
+      <c r="O105">
+        <v>2252</v>
+      </c>
+      <c r="P105">
+        <v>1414.298401</v>
+      </c>
+      <c r="Q105">
+        <v>45</v>
+      </c>
+      <c r="S105">
+        <v>70.777777999999998</v>
+      </c>
+      <c r="T105">
+        <v>1.998224</v>
+      </c>
+      <c r="U105">
+        <v>48</v>
+      </c>
+      <c r="V105">
+        <v>2.1314389999999999</v>
+      </c>
+      <c r="W105">
+        <v>66.354167000000004</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" t="s">
+        <v>145</v>
+      </c>
+      <c r="D106" t="s">
+        <v>144</v>
+      </c>
+      <c r="E106" t="s">
+        <v>29</v>
+      </c>
+      <c r="F106">
+        <v>91</v>
+      </c>
+      <c r="G106" t="s">
+        <v>41</v>
+      </c>
+      <c r="H106">
+        <v>2231</v>
+      </c>
+      <c r="I106">
+        <v>1.2438370000000001</v>
+      </c>
+      <c r="J106">
+        <v>49.912087909999997</v>
+      </c>
+      <c r="K106" t="s">
+        <v>42</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>4542</v>
+      </c>
+      <c r="N106" t="s">
+        <v>142</v>
+      </c>
+      <c r="O106">
+        <v>2775</v>
+      </c>
+      <c r="P106">
+        <v>1636.7567570000001</v>
+      </c>
+      <c r="Q106">
+        <v>103</v>
+      </c>
+      <c r="S106">
+        <v>44.097087000000002</v>
+      </c>
+      <c r="T106">
+        <v>3.7117119999999999</v>
+      </c>
+      <c r="U106">
+        <v>122</v>
+      </c>
+      <c r="V106">
+        <v>4.3963960000000002</v>
+      </c>
+      <c r="W106">
+        <v>37.229508000000003</v>
+      </c>
+      <c r="X106">
+        <v>91</v>
+      </c>
+      <c r="Y106">
+        <v>49.912087999999997</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>25</v>
+      </c>
+      <c r="B107" t="s">
+        <v>26</v>
+      </c>
+      <c r="C107" t="s">
+        <v>143</v>
+      </c>
+      <c r="D107" t="s">
+        <v>45</v>
+      </c>
+      <c r="E107" t="s">
+        <v>29</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="K107" t="s">
+        <v>42</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107" t="s">
+        <v>142</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+      <c r="U107">
+        <v>0</v>
+      </c>
+      <c r="V107">
+        <v>0</v>
+      </c>
+      <c r="W107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>25</v>
+      </c>
+      <c r="B108" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" t="s">
+        <v>141</v>
+      </c>
+      <c r="D108" t="s">
+        <v>28</v>
+      </c>
+      <c r="E108" t="s">
+        <v>29</v>
+      </c>
+      <c r="F108">
+        <v>145</v>
+      </c>
+      <c r="G108" t="s">
+        <v>41</v>
+      </c>
+      <c r="H108">
+        <v>4340</v>
+      </c>
+      <c r="I108">
+        <v>1.5082949999999999</v>
+      </c>
+      <c r="J108">
+        <v>37.16551724</v>
+      </c>
+      <c r="K108" t="s">
+        <v>42</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>5389</v>
+      </c>
+      <c r="N108" t="s">
+        <v>65</v>
+      </c>
+      <c r="O108">
+        <v>6546</v>
+      </c>
+      <c r="P108">
+        <v>823.25084000000004</v>
+      </c>
+      <c r="Q108">
+        <v>156</v>
+      </c>
+      <c r="S108">
+        <v>34.544871999999998</v>
+      </c>
+      <c r="T108">
+        <v>2.3831349999999998</v>
+      </c>
+      <c r="U108">
+        <v>174</v>
+      </c>
+      <c r="V108">
+        <v>2.658112</v>
+      </c>
+      <c r="W108">
+        <v>30.971264000000001</v>
+      </c>
+      <c r="X108">
+        <v>145</v>
+      </c>
+      <c r="Y108">
+        <v>37.165517000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>25</v>
+      </c>
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" t="s">
+        <v>140</v>
+      </c>
+      <c r="D109" t="s">
+        <v>28</v>
+      </c>
+      <c r="E109" t="s">
+        <v>29</v>
+      </c>
+      <c r="F109">
+        <v>41</v>
+      </c>
+      <c r="G109" t="s">
+        <v>41</v>
+      </c>
+      <c r="H109">
+        <v>3732</v>
+      </c>
+      <c r="I109">
+        <v>1.5535909999999999</v>
+      </c>
+      <c r="J109">
+        <v>151.48780488</v>
+      </c>
+      <c r="K109" t="s">
+        <v>42</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>6211</v>
+      </c>
+      <c r="N109" t="s">
+        <v>73</v>
+      </c>
+      <c r="O109">
+        <v>5798</v>
+      </c>
+      <c r="P109">
+        <v>1071.2314590000001</v>
+      </c>
+      <c r="Q109">
+        <v>72</v>
+      </c>
+      <c r="S109">
+        <v>86.263889000000006</v>
+      </c>
+      <c r="T109">
+        <v>1.241808</v>
+      </c>
+      <c r="U109">
+        <v>81</v>
+      </c>
+      <c r="V109">
+        <v>1.397033</v>
+      </c>
+      <c r="W109">
+        <v>76.679012</v>
+      </c>
+      <c r="X109">
+        <v>41</v>
+      </c>
+      <c r="Y109">
+        <v>151.48780500000001</v>
       </c>
     </row>
   </sheetData>
